--- a/돌발 노출 조건 정리.xlsx
+++ b/돌발 노출 조건 정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dksru\Desktop\NanseExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3E3CBB-B220-4F84-A3CF-57EEE2C9AA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388D7BF3-6A14-41DC-B6DE-2F34BD64100F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{03183270-ED35-4CBA-B934-C51A3B93B442}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="85">
   <si>
     <r>
       <t>도철</t>
@@ -658,6 +658,14 @@
   </si>
   <si>
     <t>근세1 (121)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>절멸타 확률</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>절멸타 데미지(%)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -711,7 +719,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -779,12 +787,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -888,7 +890,7 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1207,7 +1209,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC82A37B-0B66-4CDB-9A3B-3E95B08BB5E5}">
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:W32"/>
   <sheetFormatPr defaultColWidth="3.375" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="5.25" style="8" bestFit="1" customWidth="1"/>
@@ -1219,18 +1221,20 @@
     <col min="8" max="8" width="14.375" style="8" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.625" style="8" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.875" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.125" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="14.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.125" style="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.875" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="19" width="14.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.25" style="8" customWidth="1"/>
+    <col min="25" max="25" width="4" style="8" customWidth="1"/>
     <col min="26" max="27" width="3.375" style="8"/>
-    <col min="28" max="28" width="17.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.5" style="8" customWidth="1"/>
     <col min="29" max="16384" width="3.375" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="5" customFormat="1">
+    <row r="1" spans="1:23" s="5" customFormat="1">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>20</v>
@@ -1259,41 +1263,47 @@
       <c r="J1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="M1" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="N1" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="O1" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="P1" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="Q1" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="R1" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="S1" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="T1" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="S1" s="11" t="s">
+      <c r="U1" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="T1" s="11" t="s">
+      <c r="V1" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="W1" s="12" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="6" customFormat="1">
+    <row r="2" spans="1:23" s="6" customFormat="1">
       <c r="A2" s="6" t="s">
         <v>16</v>
       </c>
@@ -1324,41 +1334,47 @@
       <c r="J2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="N2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="O2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="P2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="Q2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="R2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="Q2" s="14" t="s">
+      <c r="S2" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="T2" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="U2" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="V2" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="W2" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:23">
       <c r="A3" s="7">
         <v>1</v>
       </c>
@@ -1380,8 +1396,8 @@
       <c r="G3" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="14">
-        <v>100</v>
+      <c r="H3" s="21">
+        <v>200</v>
       </c>
       <c r="I3" s="13">
         <v>1</v>
@@ -1389,41 +1405,47 @@
       <c r="J3" s="20">
         <v>0</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="K3" s="13">
+        <v>1</v>
+      </c>
+      <c r="L3" s="20">
+        <v>0</v>
+      </c>
+      <c r="M3" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="L3" s="13">
+      <c r="N3" s="13">
         <v>2000</v>
       </c>
-      <c r="M3" s="13">
+      <c r="O3" s="13">
         <v>2000</v>
       </c>
-      <c r="N3" s="13">
+      <c r="P3" s="13">
         <v>1000</v>
       </c>
-      <c r="O3" s="13">
+      <c r="Q3" s="13">
         <v>1000</v>
       </c>
-      <c r="P3" s="21">
+      <c r="R3" s="13">
         <v>300</v>
       </c>
-      <c r="Q3" s="18">
+      <c r="S3" s="18">
         <v>200</v>
       </c>
-      <c r="R3" s="8">
+      <c r="T3" s="16">
         <v>4</v>
       </c>
-      <c r="S3" s="8">
+      <c r="U3" s="13">
         <v>10</v>
       </c>
-      <c r="T3" s="8">
+      <c r="V3" s="16">
         <v>5</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="W3" s="17" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:23">
       <c r="A4" s="7">
         <v>2</v>
       </c>
@@ -1445,8 +1467,8 @@
       <c r="G4" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="14">
-        <v>200</v>
+      <c r="H4" s="21">
+        <v>400</v>
       </c>
       <c r="I4" s="13">
         <v>100</v>
@@ -1454,41 +1476,47 @@
       <c r="J4" s="20">
         <v>250</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="K4" s="13">
+        <v>100</v>
+      </c>
+      <c r="L4" s="20">
+        <v>250</v>
+      </c>
+      <c r="M4" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="L4" s="13">
+      <c r="N4" s="13">
         <v>4000</v>
       </c>
-      <c r="M4" s="13">
+      <c r="O4" s="13">
         <v>4000</v>
       </c>
-      <c r="N4" s="13">
+      <c r="P4" s="13">
         <v>3000</v>
       </c>
-      <c r="O4" s="13">
+      <c r="Q4" s="13">
         <v>3000</v>
       </c>
-      <c r="P4" s="8">
+      <c r="R4" s="13">
+        <v>2000</v>
+      </c>
+      <c r="S4" s="18">
         <v>1000</v>
       </c>
-      <c r="Q4" s="18">
-        <v>1000</v>
-      </c>
-      <c r="R4" s="8">
+      <c r="T4" s="16">
         <v>10</v>
       </c>
-      <c r="S4" s="8">
+      <c r="U4" s="13">
         <v>30</v>
       </c>
-      <c r="T4" s="8">
+      <c r="V4" s="16">
         <v>20</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="W4" s="17" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:23">
       <c r="A5" s="7">
         <v>3</v>
       </c>
@@ -1510,8 +1538,8 @@
       <c r="G5" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="14">
-        <v>400</v>
+      <c r="H5" s="21">
+        <v>800</v>
       </c>
       <c r="I5" s="13">
         <v>200</v>
@@ -1519,41 +1547,47 @@
       <c r="J5" s="20">
         <v>500</v>
       </c>
-      <c r="K5" s="16" t="s">
+      <c r="K5" s="13">
+        <v>200</v>
+      </c>
+      <c r="L5" s="20">
+        <v>500</v>
+      </c>
+      <c r="M5" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="L5" s="13">
+      <c r="N5" s="13">
         <v>12000</v>
       </c>
-      <c r="M5" s="13">
+      <c r="O5" s="13">
         <v>12000</v>
       </c>
-      <c r="N5" s="13">
+      <c r="P5" s="13">
         <v>7000</v>
       </c>
-      <c r="O5" s="13">
+      <c r="Q5" s="13">
         <v>7000</v>
       </c>
-      <c r="P5" s="8">
-        <v>2000</v>
-      </c>
-      <c r="Q5" s="18">
+      <c r="R5" s="13">
+        <v>5000</v>
+      </c>
+      <c r="S5" s="18">
         <v>3000</v>
       </c>
-      <c r="R5" s="8">
+      <c r="T5" s="16">
         <v>16</v>
       </c>
-      <c r="S5" s="8">
+      <c r="U5" s="13">
         <v>50</v>
       </c>
-      <c r="T5" s="8">
+      <c r="V5" s="16">
         <v>35</v>
       </c>
-      <c r="U5" s="1" t="s">
+      <c r="W5" s="17" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:23">
       <c r="A6" s="7">
         <v>4</v>
       </c>
@@ -1575,8 +1609,8 @@
       <c r="G6" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="14">
-        <v>600</v>
+      <c r="H6" s="21">
+        <v>1200</v>
       </c>
       <c r="I6" s="13">
         <v>300</v>
@@ -1584,41 +1618,47 @@
       <c r="J6" s="20">
         <v>750</v>
       </c>
-      <c r="K6" s="16" t="s">
+      <c r="K6" s="13">
+        <v>300</v>
+      </c>
+      <c r="L6" s="20">
+        <v>750</v>
+      </c>
+      <c r="M6" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="L6" s="13">
+      <c r="N6" s="13">
         <v>22000</v>
       </c>
-      <c r="M6" s="13">
+      <c r="O6" s="13">
         <v>22000</v>
       </c>
-      <c r="N6" s="13">
+      <c r="P6" s="13">
         <v>13000</v>
       </c>
-      <c r="O6" s="13">
+      <c r="Q6" s="13">
         <v>13000</v>
       </c>
-      <c r="P6" s="8">
-        <v>3000</v>
-      </c>
-      <c r="Q6" s="18">
+      <c r="R6" s="13">
+        <v>10000</v>
+      </c>
+      <c r="S6" s="18">
         <v>5000</v>
       </c>
-      <c r="R6" s="8">
+      <c r="T6" s="16">
         <v>22</v>
       </c>
-      <c r="S6" s="8">
+      <c r="U6" s="13">
         <v>70</v>
       </c>
-      <c r="T6" s="8">
+      <c r="V6" s="16">
         <v>50</v>
       </c>
-      <c r="U6" s="1" t="s">
+      <c r="W6" s="17" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:23">
       <c r="A7" s="7">
         <v>5</v>
       </c>
@@ -1640,50 +1680,56 @@
       <c r="G7" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="14">
-        <v>800</v>
+      <c r="H7" s="21">
+        <v>1600</v>
       </c>
       <c r="I7" s="13">
         <v>400</v>
       </c>
-      <c r="J7" s="20">
+      <c r="J7" s="13">
         <v>1000</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="K7" s="13">
+        <v>400</v>
+      </c>
+      <c r="L7" s="13">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="L7" s="13">
+      <c r="N7" s="13">
         <v>40000</v>
       </c>
-      <c r="M7" s="13">
+      <c r="O7" s="13">
         <v>40000</v>
       </c>
-      <c r="N7" s="13">
+      <c r="P7" s="13">
         <v>25000</v>
       </c>
-      <c r="O7" s="13">
+      <c r="Q7" s="13">
         <v>25000</v>
       </c>
-      <c r="P7" s="8">
-        <v>5000</v>
-      </c>
-      <c r="Q7" s="18">
+      <c r="R7" s="13">
+        <v>20000</v>
+      </c>
+      <c r="S7" s="18">
         <v>7000</v>
       </c>
-      <c r="R7" s="8">
+      <c r="T7" s="16">
         <v>28</v>
       </c>
-      <c r="S7" s="8">
+      <c r="U7" s="13">
         <v>90</v>
       </c>
-      <c r="T7" s="8">
+      <c r="V7" s="16">
         <v>65</v>
       </c>
-      <c r="U7" s="1" t="s">
+      <c r="W7" s="17" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:23">
       <c r="A8" s="7">
         <v>6</v>
       </c>
@@ -1705,8 +1751,8 @@
       <c r="G8" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="14">
-        <v>1000</v>
+      <c r="H8" s="21">
+        <v>2000</v>
       </c>
       <c r="I8" s="13">
         <v>500</v>
@@ -1714,41 +1760,47 @@
       <c r="J8" s="20">
         <v>1250</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="K8" s="13">
+        <v>500</v>
+      </c>
+      <c r="L8" s="20">
+        <v>1250</v>
+      </c>
+      <c r="M8" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L8" s="13">
+      <c r="N8" s="13">
         <v>58000</v>
       </c>
-      <c r="M8" s="13">
+      <c r="O8" s="13">
         <v>58000</v>
       </c>
-      <c r="N8" s="13">
+      <c r="P8" s="13">
         <v>37000</v>
       </c>
-      <c r="O8" s="13">
+      <c r="Q8" s="13">
         <v>37000</v>
       </c>
-      <c r="P8" s="8">
-        <v>7000</v>
-      </c>
-      <c r="Q8" s="18">
+      <c r="R8" s="13">
+        <v>30000</v>
+      </c>
+      <c r="S8" s="18">
         <v>9000</v>
       </c>
-      <c r="R8" s="8">
+      <c r="T8" s="16">
         <v>34</v>
       </c>
-      <c r="S8" s="8">
-        <v>100</v>
-      </c>
-      <c r="T8" s="8">
+      <c r="U8" s="13">
+        <v>110</v>
+      </c>
+      <c r="V8" s="16">
         <v>80</v>
       </c>
-      <c r="U8" s="1" t="s">
+      <c r="W8" s="17" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:23">
       <c r="A9" s="7">
         <v>7</v>
       </c>
@@ -1768,8 +1820,8 @@
       <c r="G9" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="14">
-        <v>1200</v>
+      <c r="H9" s="21">
+        <v>2400</v>
       </c>
       <c r="I9" s="13">
         <v>600</v>
@@ -1777,41 +1829,47 @@
       <c r="J9" s="20">
         <v>1500</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="K9" s="13">
+        <v>600</v>
+      </c>
+      <c r="L9" s="20">
+        <v>1500</v>
+      </c>
+      <c r="M9" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="L9" s="13">
+      <c r="N9" s="13">
         <v>76000</v>
       </c>
-      <c r="M9" s="13">
+      <c r="O9" s="13">
         <v>76000</v>
       </c>
-      <c r="N9" s="13">
+      <c r="P9" s="13">
         <v>49000</v>
       </c>
-      <c r="O9" s="13">
+      <c r="Q9" s="13">
         <v>49000</v>
       </c>
-      <c r="P9" s="8">
-        <v>10000</v>
-      </c>
-      <c r="Q9" s="18">
+      <c r="R9" s="13">
+        <v>40000</v>
+      </c>
+      <c r="S9" s="18">
         <v>11000</v>
       </c>
-      <c r="R9" s="8">
+      <c r="T9" s="16">
         <v>40</v>
       </c>
-      <c r="S9" s="8">
-        <v>110</v>
-      </c>
-      <c r="T9" s="8">
+      <c r="U9" s="13">
+        <v>130</v>
+      </c>
+      <c r="V9" s="16">
         <v>95</v>
       </c>
-      <c r="U9" s="1" t="s">
+      <c r="W9" s="17" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:23">
       <c r="A10" s="7">
         <v>8</v>
       </c>
@@ -1831,8 +1889,8 @@
       <c r="G10" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="14">
-        <v>1400</v>
+      <c r="H10" s="21">
+        <v>2800</v>
       </c>
       <c r="I10" s="13">
         <v>700</v>
@@ -1840,41 +1898,47 @@
       <c r="J10" s="20">
         <v>1750</v>
       </c>
-      <c r="K10" s="16" t="s">
+      <c r="K10" s="13">
+        <v>700</v>
+      </c>
+      <c r="L10" s="20">
+        <v>1750</v>
+      </c>
+      <c r="M10" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="L10" s="13">
+      <c r="N10" s="13">
         <v>94000</v>
       </c>
-      <c r="M10" s="13">
+      <c r="O10" s="13">
         <v>94000</v>
       </c>
-      <c r="N10" s="13">
+      <c r="P10" s="13">
         <v>61000</v>
       </c>
-      <c r="O10" s="13">
+      <c r="Q10" s="13">
         <v>61000</v>
       </c>
-      <c r="P10" s="8">
-        <v>15000</v>
-      </c>
-      <c r="Q10" s="18">
+      <c r="R10" s="13">
+        <v>50000</v>
+      </c>
+      <c r="S10" s="18">
         <v>13000</v>
       </c>
-      <c r="R10" s="8">
+      <c r="T10" s="16">
         <v>45</v>
       </c>
-      <c r="S10" s="8">
-        <v>120</v>
-      </c>
-      <c r="T10" s="8">
+      <c r="U10" s="13">
+        <v>150</v>
+      </c>
+      <c r="V10" s="16">
         <v>110</v>
       </c>
-      <c r="U10" s="1" t="s">
+      <c r="W10" s="17" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:23">
       <c r="A11" s="7">
         <v>9</v>
       </c>
@@ -1894,50 +1958,56 @@
       <c r="G11" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="14">
-        <v>1600</v>
+      <c r="H11" s="21">
+        <v>3200</v>
       </c>
       <c r="I11" s="13">
         <v>800</v>
       </c>
-      <c r="J11" s="20">
+      <c r="J11" s="13">
         <v>2000</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="K11" s="13">
+        <v>800</v>
+      </c>
+      <c r="L11" s="13">
+        <v>2000</v>
+      </c>
+      <c r="M11" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="L11" s="13">
+      <c r="N11" s="13">
         <v>112000</v>
       </c>
-      <c r="M11" s="13">
+      <c r="O11" s="13">
         <v>112000</v>
       </c>
-      <c r="N11" s="13">
+      <c r="P11" s="13">
         <v>73000</v>
       </c>
-      <c r="O11" s="13">
+      <c r="Q11" s="13">
         <v>73000</v>
       </c>
-      <c r="P11" s="8">
-        <v>20000</v>
-      </c>
-      <c r="Q11" s="18">
+      <c r="R11" s="13">
+        <v>60000</v>
+      </c>
+      <c r="S11" s="18">
         <v>15000</v>
       </c>
-      <c r="R11" s="8">
+      <c r="T11" s="16">
         <v>50</v>
       </c>
-      <c r="S11" s="8">
-        <v>130</v>
-      </c>
-      <c r="T11" s="8">
+      <c r="U11" s="13">
+        <v>170</v>
+      </c>
+      <c r="V11" s="16">
         <v>125</v>
       </c>
-      <c r="U11" s="1" t="s">
+      <c r="W11" s="17" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:23">
       <c r="A12" s="7">
         <v>10</v>
       </c>
@@ -1957,8 +2027,8 @@
       <c r="G12" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="H12" s="14">
-        <v>1800</v>
+      <c r="H12" s="21">
+        <v>3600</v>
       </c>
       <c r="I12" s="13">
         <v>900</v>
@@ -1966,41 +2036,47 @@
       <c r="J12" s="20">
         <v>2250</v>
       </c>
-      <c r="K12" s="16" t="s">
+      <c r="K12" s="13">
+        <v>900</v>
+      </c>
+      <c r="L12" s="20">
+        <v>2250</v>
+      </c>
+      <c r="M12" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="L12" s="13">
+      <c r="N12" s="13">
         <v>130000</v>
       </c>
-      <c r="M12" s="13">
+      <c r="O12" s="13">
         <v>130000</v>
       </c>
-      <c r="N12" s="13">
+      <c r="P12" s="13">
         <v>85000</v>
       </c>
-      <c r="O12" s="13">
+      <c r="Q12" s="13">
         <v>85000</v>
       </c>
-      <c r="P12" s="8">
-        <v>25000</v>
-      </c>
-      <c r="Q12" s="18">
+      <c r="R12" s="13">
+        <v>70000</v>
+      </c>
+      <c r="S12" s="18">
         <v>17000</v>
       </c>
-      <c r="R12" s="8">
+      <c r="T12" s="16">
         <v>55</v>
       </c>
-      <c r="S12" s="8">
+      <c r="U12" s="13">
+        <v>190</v>
+      </c>
+      <c r="V12" s="16">
         <v>140</v>
       </c>
-      <c r="T12" s="8">
-        <v>140</v>
-      </c>
-      <c r="U12" s="1" t="s">
+      <c r="W12" s="17" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:23">
       <c r="A13" s="7">
         <v>11</v>
       </c>
@@ -2017,8 +2093,8 @@
       <c r="G13" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="H13" s="14">
-        <v>2000</v>
+      <c r="H13" s="21">
+        <v>4000</v>
       </c>
       <c r="I13" s="13">
         <v>1000</v>
@@ -2026,41 +2102,47 @@
       <c r="J13" s="20">
         <v>2500</v>
       </c>
-      <c r="K13" s="16" t="s">
+      <c r="K13" s="13">
+        <v>1000</v>
+      </c>
+      <c r="L13" s="20">
+        <v>2500</v>
+      </c>
+      <c r="M13" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L13" s="13">
+      <c r="N13" s="13">
         <v>148000</v>
       </c>
-      <c r="M13" s="13">
+      <c r="O13" s="13">
         <v>148000</v>
       </c>
-      <c r="N13" s="13">
+      <c r="P13" s="13">
         <v>97000</v>
       </c>
-      <c r="O13" s="13">
+      <c r="Q13" s="13">
         <v>97000</v>
       </c>
-      <c r="P13" s="8">
-        <v>30000</v>
-      </c>
-      <c r="Q13" s="18">
+      <c r="R13" s="13">
+        <v>80000</v>
+      </c>
+      <c r="S13" s="18">
         <v>19000</v>
       </c>
-      <c r="R13" s="8">
+      <c r="T13" s="16">
         <v>60</v>
       </c>
-      <c r="S13" s="8">
-        <v>150</v>
-      </c>
-      <c r="T13" s="8">
+      <c r="U13" s="13">
+        <v>210</v>
+      </c>
+      <c r="V13" s="16">
         <v>155</v>
       </c>
-      <c r="U13" s="1" t="s">
+      <c r="W13" s="17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:21">
+    <row r="14" spans="1:23">
       <c r="A14" s="7">
         <v>12</v>
       </c>
@@ -2074,47 +2156,50 @@
         <v>600</v>
       </c>
       <c r="F14"/>
-      <c r="H14" s="14">
-        <v>2200</v>
+      <c r="H14" s="21">
+        <v>4400</v>
       </c>
       <c r="J14" s="20">
         <v>2750</v>
       </c>
-      <c r="K14" s="16" t="s">
+      <c r="L14" s="20">
+        <v>2750</v>
+      </c>
+      <c r="M14" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L14" s="13">
+      <c r="N14" s="13">
         <v>166000</v>
       </c>
-      <c r="M14" s="13">
+      <c r="O14" s="13">
         <v>166000</v>
       </c>
-      <c r="N14" s="13">
+      <c r="P14" s="13">
         <v>109000</v>
       </c>
-      <c r="O14" s="13">
+      <c r="Q14" s="13">
         <v>109000</v>
       </c>
-      <c r="P14" s="8">
-        <v>35000</v>
-      </c>
-      <c r="Q14" s="18">
+      <c r="R14" s="13">
+        <v>90000</v>
+      </c>
+      <c r="S14" s="18">
         <v>21000</v>
       </c>
-      <c r="R14" s="8">
+      <c r="T14" s="16">
         <v>65</v>
       </c>
-      <c r="S14" s="8">
-        <v>160</v>
-      </c>
-      <c r="T14" s="8">
+      <c r="U14" s="13">
+        <v>230</v>
+      </c>
+      <c r="V14" s="16">
         <v>170</v>
       </c>
-      <c r="U14" s="1" t="s">
+      <c r="W14" s="17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:23">
       <c r="A15" s="7">
         <v>13</v>
       </c>
@@ -2128,47 +2213,50 @@
         <v>650</v>
       </c>
       <c r="F15"/>
-      <c r="H15" s="14">
-        <v>2400</v>
-      </c>
-      <c r="J15" s="20">
+      <c r="H15" s="21">
+        <v>4800</v>
+      </c>
+      <c r="J15" s="13">
         <v>3000</v>
       </c>
-      <c r="K15" s="16" t="s">
+      <c r="L15" s="13">
+        <v>3000</v>
+      </c>
+      <c r="M15" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="L15" s="13">
+      <c r="N15" s="13">
         <v>184000</v>
       </c>
-      <c r="M15" s="13">
+      <c r="O15" s="13">
         <v>184000</v>
       </c>
-      <c r="N15" s="13">
+      <c r="P15" s="13">
         <v>121000</v>
       </c>
-      <c r="O15" s="13">
+      <c r="Q15" s="13">
         <v>121000</v>
       </c>
-      <c r="P15" s="8">
-        <v>40000</v>
-      </c>
-      <c r="Q15" s="18">
+      <c r="R15" s="13">
+        <v>100000</v>
+      </c>
+      <c r="S15" s="18">
         <v>23000</v>
       </c>
-      <c r="R15" s="8">
+      <c r="T15" s="16">
         <v>70</v>
       </c>
-      <c r="S15" s="8">
-        <v>170</v>
-      </c>
-      <c r="T15" s="8">
+      <c r="U15" s="13">
+        <v>250</v>
+      </c>
+      <c r="V15" s="16">
         <v>185</v>
       </c>
-      <c r="U15" s="1" t="s">
+      <c r="W15" s="17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16" spans="1:23">
       <c r="A16" s="7">
         <v>14</v>
       </c>
@@ -2182,47 +2270,50 @@
         <v>700</v>
       </c>
       <c r="F16"/>
-      <c r="H16" s="14">
-        <v>2600</v>
+      <c r="H16" s="21">
+        <v>5200</v>
       </c>
       <c r="J16" s="20">
         <v>3250</v>
       </c>
-      <c r="K16" s="16" t="s">
+      <c r="L16" s="20">
+        <v>3250</v>
+      </c>
+      <c r="M16" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L16" s="13">
+      <c r="N16" s="13">
         <v>202000</v>
       </c>
-      <c r="M16" s="13">
+      <c r="O16" s="13">
         <v>202000</v>
       </c>
-      <c r="N16" s="13">
+      <c r="P16" s="13">
         <v>133000</v>
       </c>
-      <c r="O16" s="13">
+      <c r="Q16" s="13">
         <v>133000</v>
       </c>
-      <c r="P16" s="8">
-        <v>45000</v>
-      </c>
-      <c r="Q16" s="18">
+      <c r="R16" s="13">
+        <v>110000</v>
+      </c>
+      <c r="S16" s="18">
         <v>25000</v>
       </c>
-      <c r="R16" s="8">
+      <c r="T16" s="16">
         <v>75</v>
       </c>
-      <c r="S16" s="8">
-        <v>180</v>
-      </c>
-      <c r="T16" s="8">
+      <c r="U16" s="13">
+        <v>270</v>
+      </c>
+      <c r="V16" s="16">
         <v>200</v>
       </c>
-      <c r="U16" s="1" t="s">
+      <c r="W16" s="17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:21">
+    <row r="17" spans="1:23">
       <c r="A17" s="7">
         <v>15</v>
       </c>
@@ -2236,47 +2327,50 @@
         <v>750</v>
       </c>
       <c r="F17"/>
-      <c r="H17" s="14">
-        <v>2800</v>
+      <c r="H17" s="21">
+        <v>5600</v>
       </c>
       <c r="J17" s="20">
         <v>3500</v>
       </c>
-      <c r="K17" s="16" t="s">
+      <c r="L17" s="20">
+        <v>3500</v>
+      </c>
+      <c r="M17" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L17" s="13">
+      <c r="N17" s="13">
         <v>220000</v>
       </c>
-      <c r="M17" s="13">
+      <c r="O17" s="13">
         <v>220000</v>
       </c>
-      <c r="N17" s="13">
+      <c r="P17" s="13">
         <v>145000</v>
       </c>
-      <c r="O17" s="13">
+      <c r="Q17" s="13">
         <v>145000</v>
       </c>
-      <c r="P17" s="8">
-        <v>50000</v>
-      </c>
-      <c r="Q17" s="18">
+      <c r="R17" s="13">
+        <v>120000</v>
+      </c>
+      <c r="S17" s="18">
         <v>27000</v>
       </c>
-      <c r="R17" s="8">
+      <c r="T17" s="16">
         <v>80</v>
       </c>
-      <c r="S17" s="8">
-        <v>190</v>
-      </c>
-      <c r="T17" s="8">
+      <c r="U17" s="13">
+        <v>290</v>
+      </c>
+      <c r="V17" s="16">
         <v>215</v>
       </c>
-      <c r="U17" s="1" t="s">
+      <c r="W17" s="17" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:21">
+    <row r="18" spans="1:23">
       <c r="A18" s="7">
         <v>16</v>
       </c>
@@ -2290,47 +2384,50 @@
         <v>800</v>
       </c>
       <c r="F18"/>
-      <c r="H18" s="14">
-        <v>3000</v>
+      <c r="H18" s="21">
+        <v>6000</v>
       </c>
       <c r="J18" s="20">
         <v>3750</v>
       </c>
-      <c r="K18" s="16" t="s">
+      <c r="L18" s="20">
+        <v>3750</v>
+      </c>
+      <c r="M18" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="L18" s="13">
+      <c r="N18" s="13">
         <v>238000</v>
       </c>
-      <c r="M18" s="13">
+      <c r="O18" s="13">
         <v>238000</v>
       </c>
-      <c r="N18" s="13">
+      <c r="P18" s="13">
         <v>157000</v>
       </c>
-      <c r="O18" s="13">
+      <c r="Q18" s="13">
         <v>157000</v>
       </c>
-      <c r="P18" s="8">
-        <v>55000</v>
-      </c>
-      <c r="Q18" s="18">
+      <c r="R18" s="13">
+        <v>130000</v>
+      </c>
+      <c r="S18" s="18">
         <v>29000</v>
       </c>
-      <c r="R18" s="8">
+      <c r="T18" s="16">
         <v>85</v>
       </c>
-      <c r="S18" s="8">
-        <v>200</v>
-      </c>
-      <c r="T18" s="8">
+      <c r="U18" s="13">
+        <v>310</v>
+      </c>
+      <c r="V18" s="16">
         <v>230</v>
       </c>
-      <c r="U18" s="1" t="s">
+      <c r="W18" s="17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19" spans="1:23">
       <c r="A19" s="7">
         <v>17</v>
       </c>
@@ -2345,44 +2442,47 @@
         <v>850</v>
       </c>
       <c r="F19"/>
-      <c r="H19" s="14">
-        <v>3200</v>
-      </c>
-      <c r="J19" s="20">
+      <c r="H19" s="21">
+        <v>6400</v>
+      </c>
+      <c r="J19" s="13">
         <v>4000</v>
       </c>
-      <c r="K19" s="16" t="s">
+      <c r="L19" s="13">
+        <v>4000</v>
+      </c>
+      <c r="M19" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="L19" s="13">
+      <c r="N19" s="13">
         <v>256000</v>
       </c>
-      <c r="M19" s="13">
+      <c r="O19" s="13">
         <v>256000</v>
       </c>
-      <c r="N19" s="13">
+      <c r="P19" s="13">
         <v>169000</v>
       </c>
-      <c r="O19" s="13">
+      <c r="Q19" s="13">
         <v>169000</v>
       </c>
-      <c r="P19" s="8">
-        <v>60000</v>
-      </c>
-      <c r="Q19" s="18">
+      <c r="R19" s="13">
+        <v>140000</v>
+      </c>
+      <c r="S19" s="18">
         <v>31000</v>
       </c>
-      <c r="R19" s="8">
+      <c r="T19" s="16">
         <v>90</v>
       </c>
-      <c r="S19" s="8">
-        <v>210</v>
-      </c>
-      <c r="T19" s="8">
+      <c r="U19" s="13">
+        <v>330</v>
+      </c>
+      <c r="V19" s="16">
         <v>245</v>
       </c>
     </row>
-    <row r="20" spans="1:21">
+    <row r="20" spans="1:23">
       <c r="A20" s="7">
         <v>18</v>
       </c>
@@ -2397,44 +2497,47 @@
         <v>900</v>
       </c>
       <c r="F20"/>
-      <c r="H20" s="14">
-        <v>3400</v>
+      <c r="H20" s="21">
+        <v>6800</v>
       </c>
       <c r="J20" s="20">
         <v>4250</v>
       </c>
-      <c r="K20" s="16" t="s">
+      <c r="L20" s="20">
+        <v>4250</v>
+      </c>
+      <c r="M20" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="L20" s="13">
+      <c r="N20" s="13">
         <v>274000</v>
       </c>
-      <c r="M20" s="13">
+      <c r="O20" s="13">
         <v>274000</v>
       </c>
-      <c r="N20" s="13">
+      <c r="P20" s="13">
         <v>181000</v>
       </c>
-      <c r="O20" s="13">
+      <c r="Q20" s="13">
         <v>181000</v>
       </c>
-      <c r="P20" s="8">
-        <v>65000</v>
-      </c>
-      <c r="Q20" s="18">
+      <c r="R20" s="13">
+        <v>150000</v>
+      </c>
+      <c r="S20" s="18">
         <v>33000</v>
       </c>
-      <c r="R20" s="8">
+      <c r="T20" s="16">
         <v>95</v>
       </c>
-      <c r="S20" s="8">
-        <v>220</v>
-      </c>
-      <c r="T20" s="8">
+      <c r="U20" s="13">
+        <v>350</v>
+      </c>
+      <c r="V20" s="16">
         <v>260</v>
       </c>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21" spans="1:23">
       <c r="A21" s="7">
         <v>19</v>
       </c>
@@ -2449,41 +2552,44 @@
         <v>950</v>
       </c>
       <c r="F21"/>
-      <c r="H21" s="14">
-        <v>3600</v>
+      <c r="H21" s="21">
+        <v>7200</v>
       </c>
       <c r="J21" s="20">
         <v>4500</v>
       </c>
-      <c r="L21" s="13">
+      <c r="L21" s="20">
+        <v>4500</v>
+      </c>
+      <c r="N21" s="13">
         <v>292000</v>
       </c>
-      <c r="M21" s="13">
+      <c r="O21" s="13">
         <v>292000</v>
       </c>
-      <c r="N21" s="13">
+      <c r="P21" s="13">
         <v>193000</v>
       </c>
-      <c r="O21" s="13">
+      <c r="Q21" s="13">
         <v>193000</v>
       </c>
-      <c r="P21" s="8">
-        <v>70000</v>
-      </c>
-      <c r="Q21" s="18">
+      <c r="R21" s="13">
+        <v>160000</v>
+      </c>
+      <c r="S21" s="18">
         <v>35000</v>
       </c>
-      <c r="R21" s="8">
+      <c r="T21" s="16">
         <v>100</v>
       </c>
-      <c r="S21" s="8">
-        <v>230</v>
-      </c>
-      <c r="T21" s="8">
+      <c r="U21" s="13">
+        <v>370</v>
+      </c>
+      <c r="V21" s="16">
         <v>275</v>
       </c>
     </row>
-    <row r="22" spans="1:21">
+    <row r="22" spans="1:23">
       <c r="A22" s="7">
         <v>20</v>
       </c>
@@ -2498,42 +2604,45 @@
         <v>1000</v>
       </c>
       <c r="F22"/>
-      <c r="H22" s="14">
-        <v>3800</v>
+      <c r="H22" s="21">
+        <v>7600</v>
       </c>
       <c r="J22" s="20">
         <v>4750</v>
       </c>
-      <c r="L22" s="13">
+      <c r="L22" s="20">
+        <v>4750</v>
+      </c>
+      <c r="N22" s="13">
         <v>310000</v>
       </c>
-      <c r="M22" s="13">
+      <c r="O22" s="13">
         <v>310000</v>
       </c>
-      <c r="N22" s="13">
+      <c r="P22" s="13">
         <v>205000</v>
       </c>
-      <c r="O22" s="13">
+      <c r="Q22" s="13">
         <v>205000</v>
       </c>
-      <c r="P22" s="8">
-        <v>75000</v>
-      </c>
-      <c r="Q22" s="18">
+      <c r="R22" s="13">
+        <v>170000</v>
+      </c>
+      <c r="S22" s="18">
         <v>37000</v>
       </c>
-      <c r="R22" s="8">
+      <c r="T22" s="16">
         <v>105</v>
       </c>
-      <c r="S22" s="8">
-        <v>240</v>
-      </c>
-      <c r="T22" s="8">
+      <c r="U22" s="13">
+        <v>390</v>
+      </c>
+      <c r="V22" s="16">
         <v>290</v>
       </c>
-      <c r="U22" s="9"/>
+      <c r="W22" s="9"/>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23" spans="1:23">
       <c r="A23" s="7">
         <v>21</v>
       </c>
@@ -2548,38 +2657,38 @@
         <v>1050</v>
       </c>
       <c r="F23"/>
-      <c r="H23" s="14">
-        <v>4000</v>
-      </c>
-      <c r="L23" s="13">
+      <c r="H23" s="21">
+        <v>8000</v>
+      </c>
+      <c r="N23" s="13">
         <v>328000</v>
       </c>
-      <c r="M23" s="13">
+      <c r="O23" s="13">
         <v>328000</v>
       </c>
-      <c r="N23" s="13">
+      <c r="P23" s="13">
         <v>217000</v>
       </c>
-      <c r="O23" s="13">
+      <c r="Q23" s="13">
         <v>217000</v>
       </c>
-      <c r="P23" s="8">
-        <v>80000</v>
-      </c>
-      <c r="Q23" s="18">
+      <c r="R23" s="13">
+        <v>180000</v>
+      </c>
+      <c r="S23" s="18">
         <v>39000</v>
       </c>
-      <c r="R23" s="8">
+      <c r="T23" s="16">
         <v>110</v>
       </c>
-      <c r="S23" s="8">
-        <v>250</v>
-      </c>
-      <c r="T23" s="8">
+      <c r="U23" s="13">
+        <v>410</v>
+      </c>
+      <c r="V23" s="16">
         <v>305</v>
       </c>
     </row>
-    <row r="24" spans="1:21">
+    <row r="24" spans="1:23">
       <c r="A24" s="7">
         <v>22</v>
       </c>
@@ -2593,39 +2702,39 @@
       <c r="E24" s="16">
         <v>1100</v>
       </c>
-      <c r="H24" s="14">
-        <v>4200</v>
+      <c r="H24" s="21">
+        <v>8400</v>
       </c>
       <c r="J24" s="19"/>
-      <c r="L24" s="13">
+      <c r="N24" s="13">
         <v>346000</v>
       </c>
-      <c r="M24" s="13">
+      <c r="O24" s="13">
         <v>346000</v>
       </c>
-      <c r="N24" s="13">
+      <c r="P24" s="13">
         <v>229000</v>
       </c>
-      <c r="O24" s="13">
+      <c r="Q24" s="13">
         <v>229000</v>
       </c>
-      <c r="P24" s="8">
-        <v>85000</v>
-      </c>
-      <c r="Q24" s="18">
+      <c r="R24" s="13">
+        <v>190000</v>
+      </c>
+      <c r="S24" s="18">
         <v>41000</v>
       </c>
-      <c r="R24" s="8">
+      <c r="T24" s="16">
         <v>115</v>
       </c>
-      <c r="S24" s="8">
-        <v>260</v>
-      </c>
-      <c r="T24" s="8">
+      <c r="U24" s="13">
+        <v>430</v>
+      </c>
+      <c r="V24" s="16">
         <v>320</v>
       </c>
     </row>
-    <row r="25" spans="1:21">
+    <row r="25" spans="1:23">
       <c r="A25" s="7">
         <v>23</v>
       </c>
@@ -2639,38 +2748,38 @@
       <c r="E25" s="16">
         <v>1150</v>
       </c>
-      <c r="H25" s="14">
-        <v>4400</v>
-      </c>
-      <c r="L25" s="13">
+      <c r="H25" s="21">
+        <v>8800</v>
+      </c>
+      <c r="N25" s="13">
         <v>364000</v>
       </c>
-      <c r="M25" s="13">
+      <c r="O25" s="13">
         <v>364000</v>
       </c>
-      <c r="N25" s="13">
+      <c r="P25" s="13">
         <v>241000</v>
       </c>
-      <c r="O25" s="13">
+      <c r="Q25" s="13">
         <v>241000</v>
       </c>
-      <c r="P25" s="8">
-        <v>90000</v>
-      </c>
-      <c r="Q25" s="18">
+      <c r="R25" s="13">
+        <v>200000</v>
+      </c>
+      <c r="S25" s="18">
         <v>43000</v>
       </c>
-      <c r="R25" s="8">
+      <c r="T25" s="16">
         <v>120</v>
       </c>
-      <c r="S25" s="8">
-        <v>270</v>
-      </c>
-      <c r="T25" s="8">
+      <c r="U25" s="13">
+        <v>450</v>
+      </c>
+      <c r="V25" s="16">
         <v>335</v>
       </c>
     </row>
-    <row r="26" spans="1:21">
+    <row r="26" spans="1:23">
       <c r="A26" s="7">
         <v>24</v>
       </c>
@@ -2684,39 +2793,39 @@
       <c r="E26" s="16">
         <v>1200</v>
       </c>
-      <c r="H26" s="14">
-        <v>4600</v>
+      <c r="H26" s="21">
+        <v>9200</v>
       </c>
       <c r="J26" s="19"/>
-      <c r="L26" s="13">
+      <c r="N26" s="13">
         <v>382000</v>
       </c>
-      <c r="M26" s="13">
+      <c r="O26" s="13">
         <v>382000</v>
       </c>
-      <c r="N26" s="13">
+      <c r="P26" s="13">
         <v>253000</v>
       </c>
-      <c r="O26" s="13">
+      <c r="Q26" s="13">
         <v>253000</v>
       </c>
-      <c r="P26" s="8">
-        <v>95000</v>
-      </c>
-      <c r="Q26" s="18">
+      <c r="R26" s="13">
+        <v>210000</v>
+      </c>
+      <c r="S26" s="18">
         <v>45000</v>
       </c>
-      <c r="R26" s="8">
+      <c r="T26" s="16">
         <v>125</v>
       </c>
-      <c r="S26" s="8">
-        <v>280</v>
-      </c>
-      <c r="T26" s="8">
+      <c r="U26" s="13">
+        <v>470</v>
+      </c>
+      <c r="V26" s="16">
         <v>350</v>
       </c>
     </row>
-    <row r="27" spans="1:21">
+    <row r="27" spans="1:23">
       <c r="A27" s="7">
         <v>25</v>
       </c>
@@ -2730,38 +2839,38 @@
       <c r="E27" s="16">
         <v>1250</v>
       </c>
-      <c r="H27" s="14">
-        <v>4800</v>
-      </c>
-      <c r="L27" s="13">
+      <c r="H27" s="21">
+        <v>9600</v>
+      </c>
+      <c r="N27" s="13">
         <v>400000</v>
       </c>
-      <c r="M27" s="13">
+      <c r="O27" s="13">
         <v>400000</v>
       </c>
-      <c r="N27" s="13">
+      <c r="P27" s="13">
         <v>265000</v>
       </c>
-      <c r="O27" s="13">
+      <c r="Q27" s="13">
         <v>265000</v>
       </c>
-      <c r="P27" s="8">
-        <v>100000</v>
-      </c>
-      <c r="Q27" s="18">
+      <c r="R27" s="13">
+        <v>220000</v>
+      </c>
+      <c r="S27" s="18">
         <v>47000</v>
       </c>
-      <c r="R27" s="8">
+      <c r="T27" s="16">
         <v>130</v>
       </c>
-      <c r="S27" s="8">
-        <v>290</v>
-      </c>
-      <c r="T27" s="8">
+      <c r="U27" s="13">
+        <v>490</v>
+      </c>
+      <c r="V27" s="16">
         <v>365</v>
       </c>
     </row>
-    <row r="28" spans="1:21">
+    <row r="28" spans="1:23">
       <c r="A28" s="7">
         <v>26</v>
       </c>
@@ -2775,38 +2884,38 @@
       <c r="E28" s="16">
         <v>1300</v>
       </c>
-      <c r="H28" s="14">
-        <v>5000</v>
-      </c>
-      <c r="L28" s="13">
+      <c r="H28" s="21">
+        <v>10000</v>
+      </c>
+      <c r="N28" s="13">
         <v>418000</v>
       </c>
-      <c r="M28" s="13">
+      <c r="O28" s="13">
         <v>418000</v>
       </c>
-      <c r="N28" s="13">
+      <c r="P28" s="13">
         <v>277000</v>
       </c>
-      <c r="O28" s="13">
+      <c r="Q28" s="13">
         <v>277000</v>
       </c>
-      <c r="P28" s="8">
-        <v>105000</v>
-      </c>
-      <c r="Q28" s="18">
+      <c r="R28" s="13">
+        <v>230000</v>
+      </c>
+      <c r="S28" s="18">
         <v>49000</v>
       </c>
-      <c r="R28" s="8">
+      <c r="T28" s="16">
         <v>135</v>
       </c>
-      <c r="S28" s="8">
-        <v>300</v>
-      </c>
-      <c r="T28" s="8">
+      <c r="U28" s="13">
+        <v>510</v>
+      </c>
+      <c r="V28" s="16">
         <v>380</v>
       </c>
     </row>
-    <row r="29" spans="1:21">
+    <row r="29" spans="1:23">
       <c r="A29" s="7">
         <v>27</v>
       </c>
@@ -2820,38 +2929,38 @@
       <c r="E29" s="16">
         <v>1350</v>
       </c>
-      <c r="H29" s="14">
-        <v>5200</v>
-      </c>
-      <c r="L29" s="13">
+      <c r="H29" s="21">
+        <v>10400</v>
+      </c>
+      <c r="N29" s="13">
         <v>436000</v>
       </c>
-      <c r="M29" s="13">
+      <c r="O29" s="13">
         <v>436000</v>
       </c>
-      <c r="N29" s="13">
+      <c r="P29" s="13">
         <v>289000</v>
       </c>
-      <c r="O29" s="13">
+      <c r="Q29" s="13">
         <v>289000</v>
       </c>
-      <c r="P29" s="8">
-        <v>110000</v>
-      </c>
-      <c r="Q29" s="18">
+      <c r="R29" s="13">
+        <v>240000</v>
+      </c>
+      <c r="S29" s="18">
         <v>51000</v>
       </c>
-      <c r="R29" s="8">
+      <c r="T29" s="16">
         <v>140</v>
       </c>
-      <c r="S29" s="8">
-        <v>310</v>
-      </c>
-      <c r="T29" s="8">
+      <c r="U29" s="13">
+        <v>530</v>
+      </c>
+      <c r="V29" s="16">
         <v>395</v>
       </c>
     </row>
-    <row r="30" spans="1:21">
+    <row r="30" spans="1:23">
       <c r="A30" s="7">
         <v>28</v>
       </c>
@@ -2865,38 +2974,38 @@
       <c r="E30" s="16">
         <v>1400</v>
       </c>
-      <c r="H30" s="14">
-        <v>5400</v>
-      </c>
-      <c r="L30" s="13">
+      <c r="H30" s="21">
+        <v>10800</v>
+      </c>
+      <c r="N30" s="13">
         <v>454000</v>
       </c>
-      <c r="M30" s="13">
+      <c r="O30" s="13">
         <v>454000</v>
       </c>
-      <c r="N30" s="13">
+      <c r="P30" s="13">
         <v>301000</v>
       </c>
-      <c r="O30" s="13">
+      <c r="Q30" s="13">
         <v>301000</v>
       </c>
-      <c r="P30" s="8">
-        <v>115000</v>
-      </c>
-      <c r="Q30" s="18">
+      <c r="R30" s="13">
+        <v>250000</v>
+      </c>
+      <c r="S30" s="18">
         <v>53000</v>
       </c>
-      <c r="R30" s="8">
+      <c r="T30" s="16">
         <v>145</v>
       </c>
-      <c r="S30" s="8">
-        <v>320</v>
-      </c>
-      <c r="T30" s="8">
+      <c r="U30" s="13">
+        <v>550</v>
+      </c>
+      <c r="V30" s="16">
         <v>410</v>
       </c>
     </row>
-    <row r="31" spans="1:21">
+    <row r="31" spans="1:23">
       <c r="A31" s="7">
         <v>29</v>
       </c>
@@ -2910,38 +3019,38 @@
       <c r="E31" s="16">
         <v>1450</v>
       </c>
-      <c r="H31" s="14">
-        <v>5600</v>
-      </c>
-      <c r="L31" s="13">
+      <c r="H31" s="21">
+        <v>11200</v>
+      </c>
+      <c r="N31" s="13">
         <v>472000</v>
       </c>
-      <c r="M31" s="13">
+      <c r="O31" s="13">
         <v>472000</v>
       </c>
-      <c r="N31" s="13">
+      <c r="P31" s="13">
         <v>313000</v>
       </c>
-      <c r="O31" s="13">
+      <c r="Q31" s="13">
         <v>313000</v>
       </c>
-      <c r="P31" s="8">
-        <v>120000</v>
-      </c>
-      <c r="Q31" s="18">
+      <c r="R31" s="13">
+        <v>260000</v>
+      </c>
+      <c r="S31" s="18">
         <v>55000</v>
       </c>
-      <c r="R31" s="8">
+      <c r="T31" s="16">
         <v>150</v>
       </c>
-      <c r="S31" s="8">
-        <v>330</v>
-      </c>
-      <c r="T31" s="8">
+      <c r="U31" s="13">
+        <v>570</v>
+      </c>
+      <c r="V31" s="16">
         <v>425</v>
       </c>
     </row>
-    <row r="32" spans="1:21">
+    <row r="32" spans="1:23">
       <c r="A32" s="7">
         <v>30</v>
       </c>
@@ -2955,20 +3064,35 @@
       <c r="E32" s="16">
         <v>1500</v>
       </c>
-      <c r="L32" s="13">
+      <c r="H32" s="21">
+        <v>11600</v>
+      </c>
+      <c r="N32" s="13">
         <v>490000</v>
       </c>
-      <c r="M32" s="13">
+      <c r="O32" s="13">
         <v>490000</v>
       </c>
-      <c r="N32" s="13">
+      <c r="P32" s="13">
         <v>325000</v>
       </c>
-      <c r="O32" s="13">
+      <c r="Q32" s="13">
         <v>325000</v>
       </c>
-      <c r="Q32" s="18">
+      <c r="R32" s="13">
+        <v>270000</v>
+      </c>
+      <c r="S32" s="18">
         <v>57000</v>
+      </c>
+      <c r="T32" s="16">
+        <v>155</v>
+      </c>
+      <c r="U32" s="13">
+        <v>590</v>
+      </c>
+      <c r="V32" s="16">
+        <v>440</v>
       </c>
     </row>
   </sheetData>

--- a/돌발 노출 조건 정리.xlsx
+++ b/돌발 노출 조건 정리.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dksru\Desktop\NanseExcel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dksru_vmrc15d\OneDrive\Desktop\NanseExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388D7BF3-6A14-41DC-B6DE-2F34BD64100F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42AB0D50-D7DD-4501-8199-904F6FDC3354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{03183270-ED35-4CBA-B934-C51A3B93B442}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{03183270-ED35-4CBA-B934-C51A3B93B442}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="91">
   <si>
     <r>
       <t>도철</t>
@@ -668,12 +668,36 @@
     <t>절멸타 데미지(%)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>2차</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가작업 필요</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>가격 조정</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>초반빼고</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>임의조정함</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>초반 고민</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -713,6 +737,15 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
@@ -786,12 +819,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -814,8 +846,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -825,8 +872,11 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -887,14 +937,24 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="계산" xfId="3" builtinId="22"/>
     <cellStyle name="나쁨" xfId="1" builtinId="27"/>
     <cellStyle name="보통" xfId="2" builtinId="28"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -913,9 +973,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -953,7 +1013,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1059,7 +1119,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1201,7 +1261,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1209,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC82A37B-0B66-4CDB-9A3B-3E95B08BB5E5}">
-  <dimension ref="A1:W32"/>
+  <dimension ref="A1:W33"/>
   <sheetFormatPr defaultColWidth="3.375" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="5.25" style="8" bestFit="1" customWidth="1"/>
@@ -1221,11 +1281,13 @@
     <col min="8" max="8" width="14.375" style="8" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.625" style="8" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.875" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14" style="8" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.875" style="8" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.125" style="8" bestFit="1" customWidth="1"/>
     <col min="14" max="19" width="14.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14" style="8" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.625" style="8" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="17.125" style="8" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="4.25" style="8" customWidth="1"/>
     <col min="25" max="25" width="4" style="8" customWidth="1"/>
@@ -1378,7 +1440,7 @@
       <c r="A3" s="7">
         <v>1</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="13">
         <v>60</v>
       </c>
       <c r="C3" s="16">
@@ -1396,34 +1458,34 @@
       <c r="G3" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="21">
+      <c r="H3" s="20">
         <v>200</v>
       </c>
       <c r="I3" s="13">
         <v>1</v>
       </c>
-      <c r="J3" s="20">
-        <v>0</v>
+      <c r="J3" s="13">
+        <v>1000</v>
       </c>
       <c r="K3" s="13">
         <v>1</v>
       </c>
-      <c r="L3" s="20">
-        <v>0</v>
+      <c r="L3" s="13">
+        <v>1000</v>
       </c>
       <c r="M3" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="N3" s="13">
+      <c r="N3" s="22">
         <v>2000</v>
       </c>
-      <c r="O3" s="13">
+      <c r="O3" s="22">
         <v>2000</v>
       </c>
-      <c r="P3" s="13">
+      <c r="P3" s="22">
         <v>1000</v>
       </c>
-      <c r="Q3" s="13">
+      <c r="Q3" s="22">
         <v>1000</v>
       </c>
       <c r="R3" s="13">
@@ -1449,11 +1511,11 @@
       <c r="A4" s="7">
         <v>2</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="13">
         <v>90</v>
       </c>
       <c r="C4" s="16">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="D4" s="17">
         <v>85</v>
@@ -1467,35 +1529,35 @@
       <c r="G4" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="20">
         <v>400</v>
       </c>
       <c r="I4" s="13">
         <v>100</v>
       </c>
-      <c r="J4" s="20">
-        <v>250</v>
+      <c r="J4" s="13">
+        <v>2000</v>
       </c>
       <c r="K4" s="13">
         <v>100</v>
       </c>
-      <c r="L4" s="20">
-        <v>250</v>
+      <c r="L4" s="13">
+        <v>2000</v>
       </c>
       <c r="M4" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="N4" s="13">
-        <v>4000</v>
-      </c>
-      <c r="O4" s="13">
-        <v>4000</v>
-      </c>
-      <c r="P4" s="13">
+      <c r="N4" s="22">
         <v>3000</v>
       </c>
-      <c r="Q4" s="13">
+      <c r="O4" s="22">
         <v>3000</v>
+      </c>
+      <c r="P4" s="22">
+        <v>2000</v>
+      </c>
+      <c r="Q4" s="22">
+        <v>2000</v>
       </c>
       <c r="R4" s="13">
         <v>2000</v>
@@ -1520,7 +1582,7 @@
       <c r="A5" s="7">
         <v>3</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="13">
         <v>120</v>
       </c>
       <c r="C5" s="16">
@@ -1538,35 +1600,35 @@
       <c r="G5" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="21">
+      <c r="H5" s="20">
         <v>800</v>
       </c>
       <c r="I5" s="13">
         <v>200</v>
       </c>
-      <c r="J5" s="20">
-        <v>500</v>
+      <c r="J5" s="13">
+        <v>3000</v>
       </c>
       <c r="K5" s="13">
         <v>200</v>
       </c>
-      <c r="L5" s="20">
-        <v>500</v>
+      <c r="L5" s="13">
+        <v>3000</v>
       </c>
       <c r="M5" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="N5" s="13">
-        <v>12000</v>
-      </c>
-      <c r="O5" s="13">
-        <v>12000</v>
-      </c>
-      <c r="P5" s="13">
-        <v>7000</v>
-      </c>
-      <c r="Q5" s="13">
-        <v>7000</v>
+      <c r="N5" s="22">
+        <v>4000</v>
+      </c>
+      <c r="O5" s="22">
+        <v>4000</v>
+      </c>
+      <c r="P5" s="22">
+        <v>3000</v>
+      </c>
+      <c r="Q5" s="22">
+        <v>3000</v>
       </c>
       <c r="R5" s="13">
         <v>5000</v>
@@ -1591,7 +1653,7 @@
       <c r="A6" s="7">
         <v>4</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="13">
         <v>180</v>
       </c>
       <c r="C6" s="16">
@@ -1609,35 +1671,35 @@
       <c r="G6" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="20">
         <v>1200</v>
       </c>
       <c r="I6" s="13">
         <v>300</v>
       </c>
-      <c r="J6" s="20">
-        <v>750</v>
+      <c r="J6" s="13">
+        <v>4000</v>
       </c>
       <c r="K6" s="13">
         <v>300</v>
       </c>
-      <c r="L6" s="20">
-        <v>750</v>
+      <c r="L6" s="13">
+        <v>4000</v>
       </c>
       <c r="M6" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="N6" s="13">
-        <v>22000</v>
-      </c>
-      <c r="O6" s="13">
-        <v>22000</v>
-      </c>
-      <c r="P6" s="13">
-        <v>13000</v>
-      </c>
-      <c r="Q6" s="13">
-        <v>13000</v>
+      <c r="N6" s="22">
+        <v>8000</v>
+      </c>
+      <c r="O6" s="22">
+        <v>8000</v>
+      </c>
+      <c r="P6" s="22">
+        <v>5000</v>
+      </c>
+      <c r="Q6" s="22">
+        <v>5000</v>
       </c>
       <c r="R6" s="13">
         <v>10000</v>
@@ -1662,8 +1724,8 @@
       <c r="A7" s="7">
         <v>5</v>
       </c>
-      <c r="B7" s="16">
-        <v>210</v>
+      <c r="B7" s="13">
+        <v>240</v>
       </c>
       <c r="C7" s="16">
         <v>300</v>
@@ -1680,35 +1742,35 @@
       <c r="G7" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="20">
         <v>1600</v>
       </c>
       <c r="I7" s="13">
         <v>400</v>
       </c>
-      <c r="J7" s="13">
-        <v>1000</v>
+      <c r="J7" s="23" t="s">
+        <v>86</v>
       </c>
       <c r="K7" s="13">
         <v>400</v>
       </c>
-      <c r="L7" s="13">
-        <v>1000</v>
+      <c r="L7" s="23" t="s">
+        <v>86</v>
       </c>
       <c r="M7" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="N7" s="13">
-        <v>40000</v>
-      </c>
-      <c r="O7" s="13">
-        <v>40000</v>
-      </c>
-      <c r="P7" s="13">
-        <v>25000</v>
-      </c>
-      <c r="Q7" s="13">
-        <v>25000</v>
+      <c r="N7" s="22">
+        <v>12000</v>
+      </c>
+      <c r="O7" s="22">
+        <v>12000</v>
+      </c>
+      <c r="P7" s="22">
+        <v>7000</v>
+      </c>
+      <c r="Q7" s="22">
+        <v>7000</v>
       </c>
       <c r="R7" s="13">
         <v>20000</v>
@@ -1733,8 +1795,8 @@
       <c r="A8" s="7">
         <v>6</v>
       </c>
-      <c r="B8" s="16">
-        <v>325</v>
+      <c r="B8" s="13">
+        <v>315</v>
       </c>
       <c r="C8" s="16">
         <v>350</v>
@@ -1751,35 +1813,31 @@
       <c r="G8" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="20">
         <v>2000</v>
       </c>
       <c r="I8" s="13">
         <v>500</v>
       </c>
-      <c r="J8" s="20">
-        <v>1250</v>
-      </c>
+      <c r="J8"/>
       <c r="K8" s="13">
         <v>500</v>
       </c>
-      <c r="L8" s="20">
-        <v>1250</v>
-      </c>
+      <c r="L8"/>
       <c r="M8" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="N8" s="13">
-        <v>58000</v>
-      </c>
-      <c r="O8" s="13">
-        <v>58000</v>
-      </c>
-      <c r="P8" s="13">
-        <v>37000</v>
-      </c>
-      <c r="Q8" s="13">
-        <v>37000</v>
+      <c r="N8" s="22">
+        <v>17000</v>
+      </c>
+      <c r="O8" s="22">
+        <v>17000</v>
+      </c>
+      <c r="P8" s="22">
+        <v>10000</v>
+      </c>
+      <c r="Q8" s="22">
+        <v>10000</v>
       </c>
       <c r="R8" s="13">
         <v>30000</v>
@@ -1804,8 +1862,8 @@
       <c r="A9" s="7">
         <v>7</v>
       </c>
-      <c r="B9" s="16">
-        <v>425</v>
+      <c r="B9" s="13">
+        <v>375</v>
       </c>
       <c r="C9" s="16">
         <v>400</v>
@@ -1816,39 +1874,37 @@
       <c r="E9" s="16">
         <v>350</v>
       </c>
-      <c r="F9"/>
+      <c r="F9" s="21" t="s">
+        <v>85</v>
+      </c>
       <c r="G9" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="21">
+      <c r="H9" s="20">
         <v>2400</v>
       </c>
       <c r="I9" s="13">
         <v>600</v>
       </c>
-      <c r="J9" s="20">
-        <v>1500</v>
-      </c>
+      <c r="J9"/>
       <c r="K9" s="13">
         <v>600</v>
       </c>
-      <c r="L9" s="20">
-        <v>1500</v>
-      </c>
+      <c r="L9"/>
       <c r="M9" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="N9" s="13">
-        <v>76000</v>
-      </c>
-      <c r="O9" s="13">
-        <v>76000</v>
-      </c>
-      <c r="P9" s="13">
-        <v>49000</v>
-      </c>
-      <c r="Q9" s="13">
-        <v>49000</v>
+      <c r="N9" s="22">
+        <v>22000</v>
+      </c>
+      <c r="O9" s="22">
+        <v>22000</v>
+      </c>
+      <c r="P9" s="22">
+        <v>13000</v>
+      </c>
+      <c r="Q9" s="22">
+        <v>13000</v>
       </c>
       <c r="R9" s="13">
         <v>40000</v>
@@ -1873,8 +1929,8 @@
       <c r="A10" s="7">
         <v>8</v>
       </c>
-      <c r="B10" s="16">
-        <v>525</v>
+      <c r="B10" s="13">
+        <v>435</v>
       </c>
       <c r="C10" s="16">
         <v>450</v>
@@ -1885,39 +1941,37 @@
       <c r="E10" s="16">
         <v>400</v>
       </c>
-      <c r="F10"/>
+      <c r="F10" s="22">
+        <v>300</v>
+      </c>
       <c r="G10" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="21">
+      <c r="H10" s="20">
         <v>2800</v>
       </c>
       <c r="I10" s="13">
         <v>700</v>
       </c>
-      <c r="J10" s="20">
-        <v>1750</v>
-      </c>
+      <c r="J10"/>
       <c r="K10" s="13">
         <v>700</v>
       </c>
-      <c r="L10" s="20">
-        <v>1750</v>
-      </c>
+      <c r="L10"/>
       <c r="M10" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N10" s="13">
-        <v>94000</v>
-      </c>
-      <c r="O10" s="13">
-        <v>94000</v>
-      </c>
-      <c r="P10" s="13">
-        <v>61000</v>
-      </c>
-      <c r="Q10" s="13">
-        <v>61000</v>
+      <c r="N10" s="22">
+        <v>40000</v>
+      </c>
+      <c r="O10" s="22">
+        <v>40000</v>
+      </c>
+      <c r="P10" s="22">
+        <v>25000</v>
+      </c>
+      <c r="Q10" s="22">
+        <v>25000</v>
       </c>
       <c r="R10" s="13">
         <v>50000</v>
@@ -1942,8 +1996,8 @@
       <c r="A11" s="7">
         <v>9</v>
       </c>
-      <c r="B11" s="16">
-        <v>625</v>
+      <c r="B11" s="13">
+        <v>495</v>
       </c>
       <c r="C11" s="16">
         <v>500</v>
@@ -1954,39 +2008,37 @@
       <c r="E11" s="16">
         <v>450</v>
       </c>
-      <c r="F11"/>
+      <c r="F11" s="22">
+        <v>1000</v>
+      </c>
       <c r="G11" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="21">
+      <c r="H11" s="20">
         <v>3200</v>
       </c>
       <c r="I11" s="13">
         <v>800</v>
       </c>
-      <c r="J11" s="13">
-        <v>2000</v>
-      </c>
+      <c r="J11"/>
       <c r="K11" s="13">
         <v>800</v>
       </c>
-      <c r="L11" s="13">
-        <v>2000</v>
-      </c>
+      <c r="L11"/>
       <c r="M11" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="N11" s="13">
-        <v>112000</v>
-      </c>
-      <c r="O11" s="13">
-        <v>112000</v>
-      </c>
-      <c r="P11" s="13">
-        <v>73000</v>
-      </c>
-      <c r="Q11" s="13">
-        <v>73000</v>
+      <c r="N11" s="22">
+        <v>58000</v>
+      </c>
+      <c r="O11" s="22">
+        <v>58000</v>
+      </c>
+      <c r="P11" s="22">
+        <v>37000</v>
+      </c>
+      <c r="Q11" s="22">
+        <v>37000</v>
       </c>
       <c r="R11" s="13">
         <v>60000</v>
@@ -2011,8 +2063,8 @@
       <c r="A12" s="7">
         <v>10</v>
       </c>
-      <c r="B12" s="16">
-        <v>725</v>
+      <c r="B12" s="13">
+        <v>575</v>
       </c>
       <c r="C12" s="16">
         <v>550</v>
@@ -2023,39 +2075,37 @@
       <c r="E12" s="16">
         <v>500</v>
       </c>
-      <c r="F12"/>
+      <c r="F12" s="22">
+        <v>4000</v>
+      </c>
       <c r="G12" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="20">
         <v>3600</v>
       </c>
       <c r="I12" s="13">
         <v>900</v>
       </c>
-      <c r="J12" s="20">
-        <v>2250</v>
-      </c>
+      <c r="J12"/>
       <c r="K12" s="13">
         <v>900</v>
       </c>
-      <c r="L12" s="20">
-        <v>2250</v>
-      </c>
+      <c r="L12"/>
       <c r="M12" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="N12" s="13">
-        <v>130000</v>
-      </c>
-      <c r="O12" s="13">
-        <v>130000</v>
-      </c>
-      <c r="P12" s="13">
-        <v>85000</v>
-      </c>
-      <c r="Q12" s="13">
-        <v>85000</v>
+      <c r="N12" s="22">
+        <v>76000</v>
+      </c>
+      <c r="O12" s="22">
+        <v>76000</v>
+      </c>
+      <c r="P12" s="22">
+        <v>49000</v>
+      </c>
+      <c r="Q12" s="22">
+        <v>49000</v>
       </c>
       <c r="R12" s="13">
         <v>70000</v>
@@ -2080,6 +2130,9 @@
       <c r="A13" s="7">
         <v>11</v>
       </c>
+      <c r="B13" s="23" t="s">
+        <v>89</v>
+      </c>
       <c r="C13" s="16">
         <v>600</v>
       </c>
@@ -2089,39 +2142,37 @@
       <c r="E13" s="16">
         <v>550</v>
       </c>
-      <c r="F13"/>
+      <c r="F13" s="22">
+        <v>6000</v>
+      </c>
       <c r="G13" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="H13" s="21">
+      <c r="H13" s="20">
         <v>4000</v>
       </c>
-      <c r="I13" s="13">
-        <v>1000</v>
-      </c>
-      <c r="J13" s="20">
-        <v>2500</v>
-      </c>
-      <c r="K13" s="13">
-        <v>1000</v>
-      </c>
-      <c r="L13" s="20">
-        <v>2500</v>
-      </c>
+      <c r="I13" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="J13"/>
+      <c r="K13" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="L13"/>
       <c r="M13" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="N13" s="13">
-        <v>148000</v>
-      </c>
-      <c r="O13" s="13">
-        <v>148000</v>
-      </c>
-      <c r="P13" s="13">
-        <v>97000</v>
-      </c>
-      <c r="Q13" s="13">
-        <v>97000</v>
+      <c r="N13" s="22">
+        <v>94000</v>
+      </c>
+      <c r="O13" s="22">
+        <v>94000</v>
+      </c>
+      <c r="P13" s="22">
+        <v>61000</v>
+      </c>
+      <c r="Q13" s="22">
+        <v>61000</v>
       </c>
       <c r="R13" s="13">
         <v>80000</v>
@@ -2155,30 +2206,28 @@
       <c r="E14" s="16">
         <v>600</v>
       </c>
-      <c r="F14"/>
-      <c r="H14" s="21">
+      <c r="F14" s="22">
+        <v>8000</v>
+      </c>
+      <c r="H14" s="20">
         <v>4400</v>
       </c>
-      <c r="J14" s="20">
-        <v>2750</v>
-      </c>
-      <c r="L14" s="20">
-        <v>2750</v>
-      </c>
+      <c r="J14"/>
+      <c r="L14"/>
       <c r="M14" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N14" s="13">
-        <v>166000</v>
-      </c>
-      <c r="O14" s="13">
-        <v>166000</v>
-      </c>
-      <c r="P14" s="13">
-        <v>109000</v>
-      </c>
-      <c r="Q14" s="13">
-        <v>109000</v>
+      <c r="N14" s="22">
+        <v>112000</v>
+      </c>
+      <c r="O14" s="22">
+        <v>112000</v>
+      </c>
+      <c r="P14" s="22">
+        <v>73000</v>
+      </c>
+      <c r="Q14" s="22">
+        <v>73000</v>
       </c>
       <c r="R14" s="13">
         <v>90000</v>
@@ -2212,30 +2261,28 @@
       <c r="E15" s="16">
         <v>650</v>
       </c>
-      <c r="F15"/>
-      <c r="H15" s="21">
+      <c r="F15" s="22">
+        <v>10000</v>
+      </c>
+      <c r="H15" s="20">
         <v>4800</v>
       </c>
-      <c r="J15" s="13">
-        <v>3000</v>
-      </c>
-      <c r="L15" s="13">
-        <v>3000</v>
-      </c>
+      <c r="J15"/>
+      <c r="L15"/>
       <c r="M15" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="N15" s="13">
-        <v>184000</v>
-      </c>
-      <c r="O15" s="13">
-        <v>184000</v>
-      </c>
-      <c r="P15" s="13">
-        <v>121000</v>
-      </c>
-      <c r="Q15" s="13">
-        <v>121000</v>
+      <c r="N15" s="22">
+        <v>130000</v>
+      </c>
+      <c r="O15" s="22">
+        <v>130000</v>
+      </c>
+      <c r="P15" s="22">
+        <v>85000</v>
+      </c>
+      <c r="Q15" s="22">
+        <v>85000</v>
       </c>
       <c r="R15" s="13">
         <v>100000</v>
@@ -2269,30 +2316,28 @@
       <c r="E16" s="16">
         <v>700</v>
       </c>
-      <c r="F16"/>
-      <c r="H16" s="21">
+      <c r="F16" s="22">
+        <v>12000</v>
+      </c>
+      <c r="H16" s="20">
         <v>5200</v>
       </c>
-      <c r="J16" s="20">
-        <v>3250</v>
-      </c>
-      <c r="L16" s="20">
-        <v>3250</v>
-      </c>
+      <c r="J16"/>
+      <c r="L16"/>
       <c r="M16" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="N16" s="13">
-        <v>202000</v>
-      </c>
-      <c r="O16" s="13">
-        <v>202000</v>
-      </c>
-      <c r="P16" s="13">
-        <v>133000</v>
-      </c>
-      <c r="Q16" s="13">
-        <v>133000</v>
+      <c r="N16" s="22">
+        <v>148000</v>
+      </c>
+      <c r="O16" s="22">
+        <v>148000</v>
+      </c>
+      <c r="P16" s="22">
+        <v>97000</v>
+      </c>
+      <c r="Q16" s="22">
+        <v>97000</v>
       </c>
       <c r="R16" s="13">
         <v>110000</v>
@@ -2326,30 +2371,28 @@
       <c r="E17" s="16">
         <v>750</v>
       </c>
-      <c r="F17"/>
-      <c r="H17" s="21">
+      <c r="F17" s="22">
+        <v>14000</v>
+      </c>
+      <c r="H17" s="20">
         <v>5600</v>
       </c>
-      <c r="J17" s="20">
-        <v>3500</v>
-      </c>
-      <c r="L17" s="20">
-        <v>3500</v>
-      </c>
+      <c r="J17"/>
+      <c r="L17"/>
       <c r="M17" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N17" s="13">
-        <v>220000</v>
-      </c>
-      <c r="O17" s="13">
-        <v>220000</v>
-      </c>
-      <c r="P17" s="13">
-        <v>145000</v>
-      </c>
-      <c r="Q17" s="13">
-        <v>145000</v>
+      <c r="N17" s="22">
+        <v>166000</v>
+      </c>
+      <c r="O17" s="22">
+        <v>166000</v>
+      </c>
+      <c r="P17" s="22">
+        <v>109000</v>
+      </c>
+      <c r="Q17" s="22">
+        <v>109000</v>
       </c>
       <c r="R17" s="13">
         <v>120000</v>
@@ -2383,30 +2426,28 @@
       <c r="E18" s="16">
         <v>800</v>
       </c>
-      <c r="F18"/>
-      <c r="H18" s="21">
+      <c r="F18" s="22">
+        <v>16000</v>
+      </c>
+      <c r="H18" s="20">
         <v>6000</v>
       </c>
-      <c r="J18" s="20">
-        <v>3750</v>
-      </c>
-      <c r="L18" s="20">
-        <v>3750</v>
-      </c>
+      <c r="J18"/>
+      <c r="L18"/>
       <c r="M18" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="N18" s="13">
-        <v>238000</v>
-      </c>
-      <c r="O18" s="13">
-        <v>238000</v>
-      </c>
-      <c r="P18" s="13">
-        <v>157000</v>
-      </c>
-      <c r="Q18" s="13">
-        <v>157000</v>
+      <c r="N18" s="22">
+        <v>184000</v>
+      </c>
+      <c r="O18" s="22">
+        <v>184000</v>
+      </c>
+      <c r="P18" s="22">
+        <v>121000</v>
+      </c>
+      <c r="Q18" s="22">
+        <v>121000</v>
       </c>
       <c r="R18" s="13">
         <v>130000</v>
@@ -2441,30 +2482,28 @@
       <c r="E19" s="16">
         <v>850</v>
       </c>
-      <c r="F19"/>
-      <c r="H19" s="21">
+      <c r="F19" s="22">
+        <v>18000</v>
+      </c>
+      <c r="H19" s="20">
         <v>6400</v>
       </c>
-      <c r="J19" s="13">
-        <v>4000</v>
-      </c>
-      <c r="L19" s="13">
-        <v>4000</v>
-      </c>
+      <c r="J19"/>
+      <c r="L19"/>
       <c r="M19" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="N19" s="13">
-        <v>256000</v>
-      </c>
-      <c r="O19" s="13">
-        <v>256000</v>
-      </c>
-      <c r="P19" s="13">
-        <v>169000</v>
-      </c>
-      <c r="Q19" s="13">
-        <v>169000</v>
+      <c r="N19" s="22">
+        <v>202000</v>
+      </c>
+      <c r="O19" s="22">
+        <v>202000</v>
+      </c>
+      <c r="P19" s="22">
+        <v>133000</v>
+      </c>
+      <c r="Q19" s="22">
+        <v>133000</v>
       </c>
       <c r="R19" s="13">
         <v>140000</v>
@@ -2496,30 +2535,29 @@
       <c r="E20" s="16">
         <v>900</v>
       </c>
-      <c r="F20"/>
-      <c r="H20" s="21">
+      <c r="F20" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="H20" s="20">
         <v>6800</v>
       </c>
-      <c r="J20" s="20">
-        <v>4250</v>
-      </c>
-      <c r="L20" s="20">
-        <v>4250</v>
-      </c>
+      <c r="J20"/>
+      <c r="K20"/>
+      <c r="L20"/>
       <c r="M20" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N20" s="13">
-        <v>274000</v>
-      </c>
-      <c r="O20" s="13">
-        <v>274000</v>
-      </c>
-      <c r="P20" s="13">
-        <v>181000</v>
-      </c>
-      <c r="Q20" s="13">
-        <v>181000</v>
+      <c r="N20" s="22">
+        <v>220000</v>
+      </c>
+      <c r="O20" s="22">
+        <v>220000</v>
+      </c>
+      <c r="P20" s="22">
+        <v>145000</v>
+      </c>
+      <c r="Q20" s="22">
+        <v>145000</v>
       </c>
       <c r="R20" s="13">
         <v>150000</v>
@@ -2552,26 +2590,23 @@
         <v>950</v>
       </c>
       <c r="F21"/>
-      <c r="H21" s="21">
+      <c r="H21" s="20">
         <v>7200</v>
       </c>
-      <c r="J21" s="20">
-        <v>4500</v>
-      </c>
-      <c r="L21" s="20">
-        <v>4500</v>
-      </c>
-      <c r="N21" s="13">
-        <v>292000</v>
-      </c>
-      <c r="O21" s="13">
-        <v>292000</v>
-      </c>
-      <c r="P21" s="13">
-        <v>193000</v>
-      </c>
-      <c r="Q21" s="13">
-        <v>193000</v>
+      <c r="J21"/>
+      <c r="K21"/>
+      <c r="L21"/>
+      <c r="N21" s="22">
+        <v>238000</v>
+      </c>
+      <c r="O21" s="22">
+        <v>238000</v>
+      </c>
+      <c r="P21" s="22">
+        <v>157000</v>
+      </c>
+      <c r="Q21" s="22">
+        <v>157000</v>
       </c>
       <c r="R21" s="13">
         <v>160000</v>
@@ -2604,26 +2639,23 @@
         <v>1000</v>
       </c>
       <c r="F22"/>
-      <c r="H22" s="21">
+      <c r="H22" s="20">
         <v>7600</v>
       </c>
-      <c r="J22" s="20">
-        <v>4750</v>
-      </c>
-      <c r="L22" s="20">
-        <v>4750</v>
-      </c>
-      <c r="N22" s="13">
-        <v>310000</v>
-      </c>
-      <c r="O22" s="13">
-        <v>310000</v>
-      </c>
-      <c r="P22" s="13">
-        <v>205000</v>
-      </c>
-      <c r="Q22" s="13">
-        <v>205000</v>
+      <c r="J22"/>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="N22" s="22">
+        <v>256000</v>
+      </c>
+      <c r="O22" s="22">
+        <v>256000</v>
+      </c>
+      <c r="P22" s="22">
+        <v>169000</v>
+      </c>
+      <c r="Q22" s="22">
+        <v>169000</v>
       </c>
       <c r="R22" s="13">
         <v>170000</v>
@@ -2657,20 +2689,20 @@
         <v>1050</v>
       </c>
       <c r="F23"/>
-      <c r="H23" s="21">
+      <c r="H23" s="20">
         <v>8000</v>
       </c>
-      <c r="N23" s="13">
-        <v>328000</v>
-      </c>
-      <c r="O23" s="13">
-        <v>328000</v>
-      </c>
-      <c r="P23" s="13">
-        <v>217000</v>
-      </c>
-      <c r="Q23" s="13">
-        <v>217000</v>
+      <c r="N23" s="22">
+        <v>274000</v>
+      </c>
+      <c r="O23" s="22">
+        <v>274000</v>
+      </c>
+      <c r="P23" s="22">
+        <v>181000</v>
+      </c>
+      <c r="Q23" s="22">
+        <v>181000</v>
       </c>
       <c r="R23" s="13">
         <v>180000</v>
@@ -2702,21 +2734,21 @@
       <c r="E24" s="16">
         <v>1100</v>
       </c>
-      <c r="H24" s="21">
+      <c r="H24" s="20">
         <v>8400</v>
       </c>
       <c r="J24" s="19"/>
-      <c r="N24" s="13">
-        <v>346000</v>
-      </c>
-      <c r="O24" s="13">
-        <v>346000</v>
-      </c>
-      <c r="P24" s="13">
-        <v>229000</v>
-      </c>
-      <c r="Q24" s="13">
-        <v>229000</v>
+      <c r="N24" s="22">
+        <v>292000</v>
+      </c>
+      <c r="O24" s="22">
+        <v>292000</v>
+      </c>
+      <c r="P24" s="22">
+        <v>193000</v>
+      </c>
+      <c r="Q24" s="22">
+        <v>193000</v>
       </c>
       <c r="R24" s="13">
         <v>190000</v>
@@ -2748,20 +2780,20 @@
       <c r="E25" s="16">
         <v>1150</v>
       </c>
-      <c r="H25" s="21">
+      <c r="H25" s="20">
         <v>8800</v>
       </c>
-      <c r="N25" s="13">
-        <v>364000</v>
-      </c>
-      <c r="O25" s="13">
-        <v>364000</v>
-      </c>
-      <c r="P25" s="13">
-        <v>241000</v>
-      </c>
-      <c r="Q25" s="13">
-        <v>241000</v>
+      <c r="N25" s="22">
+        <v>310000</v>
+      </c>
+      <c r="O25" s="22">
+        <v>310000</v>
+      </c>
+      <c r="P25" s="22">
+        <v>205000</v>
+      </c>
+      <c r="Q25" s="22">
+        <v>205000</v>
       </c>
       <c r="R25" s="13">
         <v>200000</v>
@@ -2793,21 +2825,21 @@
       <c r="E26" s="16">
         <v>1200</v>
       </c>
-      <c r="H26" s="21">
+      <c r="H26" s="20">
         <v>9200</v>
       </c>
       <c r="J26" s="19"/>
-      <c r="N26" s="13">
-        <v>382000</v>
-      </c>
-      <c r="O26" s="13">
-        <v>382000</v>
-      </c>
-      <c r="P26" s="13">
-        <v>253000</v>
-      </c>
-      <c r="Q26" s="13">
-        <v>253000</v>
+      <c r="N26" s="22">
+        <v>328000</v>
+      </c>
+      <c r="O26" s="22">
+        <v>328000</v>
+      </c>
+      <c r="P26" s="22">
+        <v>217000</v>
+      </c>
+      <c r="Q26" s="22">
+        <v>217000</v>
       </c>
       <c r="R26" s="13">
         <v>210000</v>
@@ -2839,20 +2871,20 @@
       <c r="E27" s="16">
         <v>1250</v>
       </c>
-      <c r="H27" s="21">
+      <c r="H27" s="20">
         <v>9600</v>
       </c>
-      <c r="N27" s="13">
-        <v>400000</v>
-      </c>
-      <c r="O27" s="13">
-        <v>400000</v>
-      </c>
-      <c r="P27" s="13">
-        <v>265000</v>
-      </c>
-      <c r="Q27" s="13">
-        <v>265000</v>
+      <c r="N27" s="22">
+        <v>346000</v>
+      </c>
+      <c r="O27" s="22">
+        <v>346000</v>
+      </c>
+      <c r="P27" s="22">
+        <v>229000</v>
+      </c>
+      <c r="Q27" s="22">
+        <v>229000</v>
       </c>
       <c r="R27" s="13">
         <v>220000</v>
@@ -2884,20 +2916,20 @@
       <c r="E28" s="16">
         <v>1300</v>
       </c>
-      <c r="H28" s="21">
+      <c r="H28" s="20">
         <v>10000</v>
       </c>
-      <c r="N28" s="13">
-        <v>418000</v>
-      </c>
-      <c r="O28" s="13">
-        <v>418000</v>
-      </c>
-      <c r="P28" s="13">
-        <v>277000</v>
-      </c>
-      <c r="Q28" s="13">
-        <v>277000</v>
+      <c r="N28" s="22">
+        <v>364000</v>
+      </c>
+      <c r="O28" s="22">
+        <v>364000</v>
+      </c>
+      <c r="P28" s="22">
+        <v>241000</v>
+      </c>
+      <c r="Q28" s="22">
+        <v>241000</v>
       </c>
       <c r="R28" s="13">
         <v>230000</v>
@@ -2929,20 +2961,20 @@
       <c r="E29" s="16">
         <v>1350</v>
       </c>
-      <c r="H29" s="21">
+      <c r="H29" s="20">
         <v>10400</v>
       </c>
-      <c r="N29" s="13">
-        <v>436000</v>
-      </c>
-      <c r="O29" s="13">
-        <v>436000</v>
-      </c>
-      <c r="P29" s="13">
-        <v>289000</v>
-      </c>
-      <c r="Q29" s="13">
-        <v>289000</v>
+      <c r="N29" s="22">
+        <v>382000</v>
+      </c>
+      <c r="O29" s="22">
+        <v>382000</v>
+      </c>
+      <c r="P29" s="22">
+        <v>253000</v>
+      </c>
+      <c r="Q29" s="22">
+        <v>253000</v>
       </c>
       <c r="R29" s="13">
         <v>240000</v>
@@ -2974,20 +3006,20 @@
       <c r="E30" s="16">
         <v>1400</v>
       </c>
-      <c r="H30" s="21">
+      <c r="H30" s="20">
         <v>10800</v>
       </c>
-      <c r="N30" s="13">
-        <v>454000</v>
-      </c>
-      <c r="O30" s="13">
-        <v>454000</v>
-      </c>
-      <c r="P30" s="13">
-        <v>301000</v>
-      </c>
-      <c r="Q30" s="13">
-        <v>301000</v>
+      <c r="N30" s="22">
+        <v>400000</v>
+      </c>
+      <c r="O30" s="22">
+        <v>400000</v>
+      </c>
+      <c r="P30" s="22">
+        <v>265000</v>
+      </c>
+      <c r="Q30" s="22">
+        <v>265000</v>
       </c>
       <c r="R30" s="13">
         <v>250000</v>
@@ -3019,20 +3051,20 @@
       <c r="E31" s="16">
         <v>1450</v>
       </c>
-      <c r="H31" s="21">
+      <c r="H31" s="20">
         <v>11200</v>
       </c>
-      <c r="N31" s="13">
-        <v>472000</v>
-      </c>
-      <c r="O31" s="13">
-        <v>472000</v>
-      </c>
-      <c r="P31" s="13">
-        <v>313000</v>
-      </c>
-      <c r="Q31" s="13">
-        <v>313000</v>
+      <c r="N31" s="22">
+        <v>418000</v>
+      </c>
+      <c r="O31" s="22">
+        <v>418000</v>
+      </c>
+      <c r="P31" s="22">
+        <v>277000</v>
+      </c>
+      <c r="Q31" s="22">
+        <v>277000</v>
       </c>
       <c r="R31" s="13">
         <v>260000</v>
@@ -3064,20 +3096,20 @@
       <c r="E32" s="16">
         <v>1500</v>
       </c>
-      <c r="H32" s="21">
+      <c r="H32" s="20">
         <v>11600</v>
       </c>
-      <c r="N32" s="13">
-        <v>490000</v>
-      </c>
-      <c r="O32" s="13">
-        <v>490000</v>
-      </c>
-      <c r="P32" s="13">
-        <v>325000</v>
-      </c>
-      <c r="Q32" s="13">
-        <v>325000</v>
+      <c r="N32" s="22">
+        <v>436000</v>
+      </c>
+      <c r="O32" s="22">
+        <v>436000</v>
+      </c>
+      <c r="P32" s="22">
+        <v>289000</v>
+      </c>
+      <c r="Q32" s="22">
+        <v>289000</v>
       </c>
       <c r="R32" s="13">
         <v>270000</v>
@@ -3093,6 +3125,29 @@
       </c>
       <c r="V32" s="16">
         <v>440</v>
+      </c>
+    </row>
+    <row r="33" spans="8:21">
+      <c r="H33" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="N33" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="O33" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="P33" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q33" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="R33" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="U33" s="23" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/돌발 노출 조건 정리.xlsx
+++ b/돌발 노출 조건 정리.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dksru_vmrc15d\OneDrive\Desktop\NanseExcel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dksru\Desktop\NanseExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42AB0D50-D7DD-4501-8199-904F6FDC3354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA2A76A-C5B0-4B15-9899-D13245E0D743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{03183270-ED35-4CBA-B934-C51A3B93B442}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{03183270-ED35-4CBA-B934-C51A3B93B442}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="89">
   <si>
     <r>
       <t>도철</t>
@@ -681,15 +681,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>초반빼고</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>임의조정함</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>초반 고민</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -697,7 +689,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -751,8 +743,15 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -822,6 +821,12 @@
         <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -862,7 +867,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -875,8 +880,9 @@
     <xf numFmtId="0" fontId="6" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -952,12 +958,23 @@
     <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="3">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="계산" xfId="3" builtinId="22"/>
     <cellStyle name="나쁨" xfId="1" builtinId="27"/>
     <cellStyle name="보통" xfId="2" builtinId="28"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="표준 2" xfId="4" xr:uid="{A35E1931-9310-4F46-A43B-E2461EFDA7B0}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -973,9 +990,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1013,7 +1030,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1119,7 +1136,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1261,7 +1278,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1476,26 +1493,26 @@
       <c r="M3" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="N3" s="22">
+      <c r="N3" s="25">
         <v>2000</v>
       </c>
-      <c r="O3" s="22">
-        <v>2000</v>
-      </c>
-      <c r="P3" s="22">
-        <v>1000</v>
-      </c>
-      <c r="Q3" s="22">
-        <v>1000</v>
-      </c>
-      <c r="R3" s="13">
+      <c r="O3" s="26">
+        <v>4000</v>
+      </c>
+      <c r="P3" s="27">
+        <v>1250</v>
+      </c>
+      <c r="Q3" s="27">
+        <v>3000</v>
+      </c>
+      <c r="R3" s="26">
         <v>300</v>
       </c>
-      <c r="S3" s="18">
+      <c r="S3" s="27">
         <v>200</v>
       </c>
       <c r="T3" s="16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U3" s="13">
         <v>10</v>
@@ -1547,26 +1564,26 @@
       <c r="M4" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="N4" s="22">
+      <c r="N4" s="25">
+        <v>4000</v>
+      </c>
+      <c r="O4" s="26">
+        <v>7000</v>
+      </c>
+      <c r="P4" s="27">
         <v>3000</v>
       </c>
-      <c r="O4" s="22">
-        <v>3000</v>
-      </c>
-      <c r="P4" s="22">
+      <c r="Q4" s="27">
+        <v>5000</v>
+      </c>
+      <c r="R4" s="26">
         <v>2000</v>
       </c>
-      <c r="Q4" s="22">
-        <v>2000</v>
-      </c>
-      <c r="R4" s="13">
-        <v>2000</v>
-      </c>
-      <c r="S4" s="18">
+      <c r="S4" s="27">
         <v>1000</v>
       </c>
       <c r="T4" s="16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U4" s="13">
         <v>30</v>
@@ -1618,26 +1635,26 @@
       <c r="M5" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="N5" s="22">
+      <c r="N5" s="25">
+        <v>7000</v>
+      </c>
+      <c r="O5" s="26">
+        <v>12000</v>
+      </c>
+      <c r="P5" s="27">
+        <v>5000</v>
+      </c>
+      <c r="Q5" s="27">
+        <v>8000</v>
+      </c>
+      <c r="R5" s="26">
         <v>4000</v>
       </c>
-      <c r="O5" s="22">
-        <v>4000</v>
-      </c>
-      <c r="P5" s="22">
-        <v>3000</v>
-      </c>
-      <c r="Q5" s="22">
-        <v>3000</v>
-      </c>
-      <c r="R5" s="13">
-        <v>5000</v>
-      </c>
-      <c r="S5" s="18">
-        <v>3000</v>
+      <c r="S5" s="27">
+        <v>2000</v>
       </c>
       <c r="T5" s="16">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U5" s="13">
         <v>50</v>
@@ -1689,26 +1706,26 @@
       <c r="M6" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="N6" s="22">
+      <c r="N6" s="25">
+        <v>12000</v>
+      </c>
+      <c r="O6" s="26">
+        <v>17000</v>
+      </c>
+      <c r="P6" s="27">
         <v>8000</v>
       </c>
-      <c r="O6" s="22">
-        <v>8000</v>
-      </c>
-      <c r="P6" s="22">
-        <v>5000</v>
-      </c>
-      <c r="Q6" s="22">
-        <v>5000</v>
-      </c>
-      <c r="R6" s="13">
-        <v>10000</v>
-      </c>
-      <c r="S6" s="18">
-        <v>5000</v>
+      <c r="Q6" s="27">
+        <v>11000</v>
+      </c>
+      <c r="R6" s="26">
+        <v>6000</v>
+      </c>
+      <c r="S6" s="27">
+        <v>3500</v>
       </c>
       <c r="T6" s="16">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U6" s="13">
         <v>70</v>
@@ -1760,26 +1777,26 @@
       <c r="M7" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="N7" s="22">
-        <v>12000</v>
-      </c>
-      <c r="O7" s="22">
-        <v>12000</v>
-      </c>
-      <c r="P7" s="22">
-        <v>7000</v>
-      </c>
-      <c r="Q7" s="22">
-        <v>7000</v>
-      </c>
-      <c r="R7" s="13">
-        <v>20000</v>
-      </c>
-      <c r="S7" s="18">
-        <v>7000</v>
+      <c r="N7" s="25">
+        <v>17000</v>
+      </c>
+      <c r="O7" s="26">
+        <v>22000</v>
+      </c>
+      <c r="P7" s="27">
+        <v>11000</v>
+      </c>
+      <c r="Q7" s="27">
+        <v>14000</v>
+      </c>
+      <c r="R7" s="26">
+        <v>13000</v>
+      </c>
+      <c r="S7" s="27">
+        <v>5500</v>
       </c>
       <c r="T7" s="16">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="U7" s="13">
         <v>90</v>
@@ -1827,26 +1844,26 @@
       <c r="M8" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="N8" s="22">
-        <v>17000</v>
-      </c>
-      <c r="O8" s="22">
-        <v>17000</v>
-      </c>
-      <c r="P8" s="22">
-        <v>10000</v>
-      </c>
-      <c r="Q8" s="22">
-        <v>10000</v>
-      </c>
-      <c r="R8" s="13">
-        <v>30000</v>
-      </c>
-      <c r="S8" s="18">
-        <v>9000</v>
+      <c r="N8" s="25">
+        <v>22000</v>
+      </c>
+      <c r="O8" s="26">
+        <v>33000</v>
+      </c>
+      <c r="P8" s="27">
+        <v>14000</v>
+      </c>
+      <c r="Q8" s="27">
+        <v>22000</v>
+      </c>
+      <c r="R8" s="26">
+        <v>20000</v>
+      </c>
+      <c r="S8" s="27">
+        <v>7500</v>
       </c>
       <c r="T8" s="16">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U8" s="13">
         <v>110</v>
@@ -1894,23 +1911,23 @@
       <c r="M9" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="N9" s="22">
+      <c r="N9" s="25">
+        <v>33000</v>
+      </c>
+      <c r="O9" s="26">
+        <v>44000</v>
+      </c>
+      <c r="P9" s="27">
         <v>22000</v>
       </c>
-      <c r="O9" s="22">
-        <v>22000</v>
-      </c>
-      <c r="P9" s="22">
-        <v>13000</v>
-      </c>
-      <c r="Q9" s="22">
-        <v>13000</v>
-      </c>
-      <c r="R9" s="13">
-        <v>40000</v>
-      </c>
-      <c r="S9" s="18">
-        <v>11000</v>
+      <c r="Q9" s="27">
+        <v>30000</v>
+      </c>
+      <c r="R9" s="26">
+        <v>27000</v>
+      </c>
+      <c r="S9" s="27">
+        <v>9500</v>
       </c>
       <c r="T9" s="16">
         <v>40</v>
@@ -1961,23 +1978,23 @@
       <c r="M10" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N10" s="22">
-        <v>40000</v>
-      </c>
-      <c r="O10" s="22">
-        <v>40000</v>
-      </c>
-      <c r="P10" s="22">
-        <v>25000</v>
-      </c>
-      <c r="Q10" s="22">
-        <v>25000</v>
-      </c>
-      <c r="R10" s="13">
-        <v>50000</v>
-      </c>
-      <c r="S10" s="18">
-        <v>13000</v>
+      <c r="N10" s="25">
+        <v>44000</v>
+      </c>
+      <c r="O10" s="26">
+        <v>55000</v>
+      </c>
+      <c r="P10" s="27">
+        <v>30000</v>
+      </c>
+      <c r="Q10" s="27">
+        <v>38000</v>
+      </c>
+      <c r="R10" s="26">
+        <v>34000</v>
+      </c>
+      <c r="S10" s="27">
+        <v>11500</v>
       </c>
       <c r="T10" s="16">
         <v>45</v>
@@ -2028,23 +2045,23 @@
       <c r="M11" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="N11" s="22">
-        <v>58000</v>
-      </c>
-      <c r="O11" s="22">
-        <v>58000</v>
-      </c>
-      <c r="P11" s="22">
-        <v>37000</v>
-      </c>
-      <c r="Q11" s="22">
-        <v>37000</v>
-      </c>
-      <c r="R11" s="13">
-        <v>60000</v>
-      </c>
-      <c r="S11" s="18">
-        <v>15000</v>
+      <c r="N11" s="25">
+        <v>55000</v>
+      </c>
+      <c r="O11" s="26">
+        <v>66000</v>
+      </c>
+      <c r="P11" s="27">
+        <v>38000</v>
+      </c>
+      <c r="Q11" s="27">
+        <v>46000</v>
+      </c>
+      <c r="R11" s="26">
+        <v>41000</v>
+      </c>
+      <c r="S11" s="27">
+        <v>13500</v>
       </c>
       <c r="T11" s="16">
         <v>50</v>
@@ -2095,23 +2112,23 @@
       <c r="M12" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="N12" s="22">
-        <v>76000</v>
-      </c>
-      <c r="O12" s="22">
-        <v>76000</v>
-      </c>
-      <c r="P12" s="22">
-        <v>49000</v>
-      </c>
-      <c r="Q12" s="22">
-        <v>49000</v>
-      </c>
-      <c r="R12" s="13">
-        <v>70000</v>
-      </c>
-      <c r="S12" s="18">
-        <v>17000</v>
+      <c r="N12" s="25">
+        <v>66000</v>
+      </c>
+      <c r="O12" s="26">
+        <v>77000</v>
+      </c>
+      <c r="P12" s="27">
+        <v>46000</v>
+      </c>
+      <c r="Q12" s="27">
+        <v>54000</v>
+      </c>
+      <c r="R12" s="26">
+        <v>48000</v>
+      </c>
+      <c r="S12" s="27">
+        <v>15500</v>
       </c>
       <c r="T12" s="16">
         <v>55</v>
@@ -2131,7 +2148,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C13" s="16">
         <v>600</v>
@@ -2162,23 +2179,23 @@
       <c r="M13" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="N13" s="22">
-        <v>94000</v>
-      </c>
-      <c r="O13" s="22">
-        <v>94000</v>
-      </c>
-      <c r="P13" s="22">
-        <v>61000</v>
-      </c>
-      <c r="Q13" s="22">
-        <v>61000</v>
-      </c>
-      <c r="R13" s="13">
-        <v>80000</v>
-      </c>
-      <c r="S13" s="18">
-        <v>19000</v>
+      <c r="N13" s="25">
+        <v>77000</v>
+      </c>
+      <c r="O13" s="26">
+        <v>88000</v>
+      </c>
+      <c r="P13" s="27">
+        <v>54000</v>
+      </c>
+      <c r="Q13" s="27">
+        <v>62000</v>
+      </c>
+      <c r="R13" s="26">
+        <v>55000</v>
+      </c>
+      <c r="S13" s="27">
+        <v>17500</v>
       </c>
       <c r="T13" s="16">
         <v>60</v>
@@ -2217,23 +2234,23 @@
       <c r="M14" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N14" s="22">
-        <v>112000</v>
-      </c>
-      <c r="O14" s="22">
-        <v>112000</v>
-      </c>
-      <c r="P14" s="22">
-        <v>73000</v>
-      </c>
-      <c r="Q14" s="22">
-        <v>73000</v>
-      </c>
-      <c r="R14" s="13">
-        <v>90000</v>
-      </c>
-      <c r="S14" s="18">
-        <v>21000</v>
+      <c r="N14" s="25">
+        <v>88000</v>
+      </c>
+      <c r="O14" s="26">
+        <v>99000</v>
+      </c>
+      <c r="P14" s="27">
+        <v>62000</v>
+      </c>
+      <c r="Q14" s="27">
+        <v>70000</v>
+      </c>
+      <c r="R14" s="26">
+        <v>62000</v>
+      </c>
+      <c r="S14" s="27">
+        <v>19500</v>
       </c>
       <c r="T14" s="16">
         <v>65</v>
@@ -2272,23 +2289,23 @@
       <c r="M15" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="N15" s="22">
-        <v>130000</v>
-      </c>
-      <c r="O15" s="22">
-        <v>130000</v>
-      </c>
-      <c r="P15" s="22">
-        <v>85000</v>
-      </c>
-      <c r="Q15" s="22">
-        <v>85000</v>
-      </c>
-      <c r="R15" s="13">
-        <v>100000</v>
-      </c>
-      <c r="S15" s="18">
-        <v>23000</v>
+      <c r="N15" s="25">
+        <v>99000</v>
+      </c>
+      <c r="O15" s="26">
+        <v>110000</v>
+      </c>
+      <c r="P15" s="27">
+        <v>70000</v>
+      </c>
+      <c r="Q15" s="27">
+        <v>78000</v>
+      </c>
+      <c r="R15" s="26">
+        <v>69000</v>
+      </c>
+      <c r="S15" s="27">
+        <v>21500</v>
       </c>
       <c r="T15" s="16">
         <v>70</v>
@@ -2327,23 +2344,23 @@
       <c r="M16" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="N16" s="22">
-        <v>148000</v>
-      </c>
-      <c r="O16" s="22">
-        <v>148000</v>
-      </c>
-      <c r="P16" s="22">
-        <v>97000</v>
-      </c>
-      <c r="Q16" s="22">
-        <v>97000</v>
-      </c>
-      <c r="R16" s="13">
+      <c r="N16" s="25">
         <v>110000</v>
       </c>
-      <c r="S16" s="18">
-        <v>25000</v>
+      <c r="O16" s="26">
+        <v>121000</v>
+      </c>
+      <c r="P16" s="27">
+        <v>78000</v>
+      </c>
+      <c r="Q16" s="27">
+        <v>86000</v>
+      </c>
+      <c r="R16" s="26">
+        <v>76000</v>
+      </c>
+      <c r="S16" s="27">
+        <v>23500</v>
       </c>
       <c r="T16" s="16">
         <v>75</v>
@@ -2382,23 +2399,23 @@
       <c r="M17" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N17" s="22">
-        <v>166000</v>
-      </c>
-      <c r="O17" s="22">
-        <v>166000</v>
-      </c>
-      <c r="P17" s="22">
-        <v>109000</v>
-      </c>
-      <c r="Q17" s="22">
-        <v>109000</v>
-      </c>
-      <c r="R17" s="13">
-        <v>120000</v>
-      </c>
-      <c r="S17" s="18">
-        <v>27000</v>
+      <c r="N17" s="25">
+        <v>121000</v>
+      </c>
+      <c r="O17" s="26">
+        <v>132000</v>
+      </c>
+      <c r="P17" s="27">
+        <v>86000</v>
+      </c>
+      <c r="Q17" s="27">
+        <v>94000</v>
+      </c>
+      <c r="R17" s="26">
+        <v>83000</v>
+      </c>
+      <c r="S17" s="27">
+        <v>25500</v>
       </c>
       <c r="T17" s="16">
         <v>80</v>
@@ -2437,23 +2454,23 @@
       <c r="M18" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="N18" s="22">
-        <v>184000</v>
-      </c>
-      <c r="O18" s="22">
-        <v>184000</v>
-      </c>
-      <c r="P18" s="22">
-        <v>121000</v>
-      </c>
-      <c r="Q18" s="22">
-        <v>121000</v>
-      </c>
-      <c r="R18" s="13">
-        <v>130000</v>
-      </c>
-      <c r="S18" s="18">
-        <v>29000</v>
+      <c r="N18" s="25">
+        <v>132000</v>
+      </c>
+      <c r="O18" s="26">
+        <v>143000</v>
+      </c>
+      <c r="P18" s="27">
+        <v>94000</v>
+      </c>
+      <c r="Q18" s="27">
+        <v>102000</v>
+      </c>
+      <c r="R18" s="26">
+        <v>90000</v>
+      </c>
+      <c r="S18" s="27">
+        <v>27500</v>
       </c>
       <c r="T18" s="16">
         <v>85</v>
@@ -2493,23 +2510,23 @@
       <c r="M19" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="N19" s="22">
-        <v>202000</v>
-      </c>
-      <c r="O19" s="22">
-        <v>202000</v>
-      </c>
-      <c r="P19" s="22">
-        <v>133000</v>
-      </c>
-      <c r="Q19" s="22">
-        <v>133000</v>
-      </c>
-      <c r="R19" s="13">
-        <v>140000</v>
-      </c>
-      <c r="S19" s="18">
-        <v>31000</v>
+      <c r="N19" s="25">
+        <v>143000</v>
+      </c>
+      <c r="O19" s="26">
+        <v>154000</v>
+      </c>
+      <c r="P19" s="27">
+        <v>102000</v>
+      </c>
+      <c r="Q19" s="27">
+        <v>110000</v>
+      </c>
+      <c r="R19" s="26">
+        <v>97000</v>
+      </c>
+      <c r="S19" s="27">
+        <v>29500</v>
       </c>
       <c r="T19" s="16">
         <v>90</v>
@@ -2536,7 +2553,7 @@
         <v>900</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H20" s="20">
         <v>6800</v>
@@ -2547,23 +2564,23 @@
       <c r="M20" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N20" s="22">
-        <v>220000</v>
-      </c>
-      <c r="O20" s="22">
-        <v>220000</v>
-      </c>
-      <c r="P20" s="22">
-        <v>145000</v>
-      </c>
-      <c r="Q20" s="22">
-        <v>145000</v>
-      </c>
-      <c r="R20" s="13">
-        <v>150000</v>
-      </c>
-      <c r="S20" s="18">
-        <v>33000</v>
+      <c r="N20" s="25">
+        <v>154000</v>
+      </c>
+      <c r="O20" s="26">
+        <v>165000</v>
+      </c>
+      <c r="P20" s="27">
+        <v>110000</v>
+      </c>
+      <c r="Q20" s="27">
+        <v>118000</v>
+      </c>
+      <c r="R20" s="26">
+        <v>104000</v>
+      </c>
+      <c r="S20" s="27">
+        <v>31500</v>
       </c>
       <c r="T20" s="16">
         <v>95</v>
@@ -2596,23 +2613,23 @@
       <c r="J21"/>
       <c r="K21"/>
       <c r="L21"/>
-      <c r="N21" s="22">
-        <v>238000</v>
-      </c>
-      <c r="O21" s="22">
-        <v>238000</v>
-      </c>
-      <c r="P21" s="22">
-        <v>157000</v>
-      </c>
-      <c r="Q21" s="22">
-        <v>157000</v>
-      </c>
-      <c r="R21" s="13">
-        <v>160000</v>
-      </c>
-      <c r="S21" s="18">
-        <v>35000</v>
+      <c r="N21" s="25">
+        <v>165000</v>
+      </c>
+      <c r="O21" s="26">
+        <v>176000</v>
+      </c>
+      <c r="P21" s="27">
+        <v>118000</v>
+      </c>
+      <c r="Q21" s="27">
+        <v>126000</v>
+      </c>
+      <c r="R21" s="26">
+        <v>111000</v>
+      </c>
+      <c r="S21" s="27">
+        <v>33500</v>
       </c>
       <c r="T21" s="16">
         <v>100</v>
@@ -2645,23 +2662,23 @@
       <c r="J22"/>
       <c r="K22"/>
       <c r="L22"/>
-      <c r="N22" s="22">
-        <v>256000</v>
-      </c>
-      <c r="O22" s="22">
-        <v>256000</v>
-      </c>
-      <c r="P22" s="22">
-        <v>169000</v>
-      </c>
-      <c r="Q22" s="22">
-        <v>169000</v>
-      </c>
-      <c r="R22" s="13">
-        <v>170000</v>
-      </c>
-      <c r="S22" s="18">
-        <v>37000</v>
+      <c r="N22" s="25">
+        <v>176000</v>
+      </c>
+      <c r="O22" s="26">
+        <v>187000</v>
+      </c>
+      <c r="P22" s="27">
+        <v>126000</v>
+      </c>
+      <c r="Q22" s="27">
+        <v>134000</v>
+      </c>
+      <c r="R22" s="26">
+        <v>118000</v>
+      </c>
+      <c r="S22" s="27">
+        <v>35500</v>
       </c>
       <c r="T22" s="16">
         <v>105</v>
@@ -2692,23 +2709,23 @@
       <c r="H23" s="20">
         <v>8000</v>
       </c>
-      <c r="N23" s="22">
-        <v>274000</v>
-      </c>
-      <c r="O23" s="22">
-        <v>274000</v>
-      </c>
-      <c r="P23" s="22">
-        <v>181000</v>
-      </c>
-      <c r="Q23" s="22">
-        <v>181000</v>
-      </c>
-      <c r="R23" s="13">
-        <v>180000</v>
-      </c>
-      <c r="S23" s="18">
-        <v>39000</v>
+      <c r="N23" s="25">
+        <v>187000</v>
+      </c>
+      <c r="O23" s="26">
+        <v>198000</v>
+      </c>
+      <c r="P23" s="27">
+        <v>134000</v>
+      </c>
+      <c r="Q23" s="27">
+        <v>142000</v>
+      </c>
+      <c r="R23" s="26">
+        <v>125000</v>
+      </c>
+      <c r="S23" s="27">
+        <v>37500</v>
       </c>
       <c r="T23" s="16">
         <v>110</v>
@@ -2738,23 +2755,23 @@
         <v>8400</v>
       </c>
       <c r="J24" s="19"/>
-      <c r="N24" s="22">
-        <v>292000</v>
-      </c>
-      <c r="O24" s="22">
-        <v>292000</v>
-      </c>
-      <c r="P24" s="22">
-        <v>193000</v>
-      </c>
-      <c r="Q24" s="22">
-        <v>193000</v>
-      </c>
-      <c r="R24" s="13">
-        <v>190000</v>
-      </c>
-      <c r="S24" s="18">
-        <v>41000</v>
+      <c r="N24" s="25">
+        <v>198000</v>
+      </c>
+      <c r="O24" s="26">
+        <v>209000</v>
+      </c>
+      <c r="P24" s="27">
+        <v>142000</v>
+      </c>
+      <c r="Q24" s="27">
+        <v>150000</v>
+      </c>
+      <c r="R24" s="26">
+        <v>132000</v>
+      </c>
+      <c r="S24" s="27">
+        <v>39500</v>
       </c>
       <c r="T24" s="16">
         <v>115</v>
@@ -2783,23 +2800,23 @@
       <c r="H25" s="20">
         <v>8800</v>
       </c>
-      <c r="N25" s="22">
-        <v>310000</v>
-      </c>
-      <c r="O25" s="22">
-        <v>310000</v>
-      </c>
-      <c r="P25" s="22">
-        <v>205000</v>
-      </c>
-      <c r="Q25" s="22">
-        <v>205000</v>
-      </c>
-      <c r="R25" s="13">
-        <v>200000</v>
-      </c>
-      <c r="S25" s="18">
-        <v>43000</v>
+      <c r="N25" s="25">
+        <v>209000</v>
+      </c>
+      <c r="O25" s="26">
+        <v>220000</v>
+      </c>
+      <c r="P25" s="27">
+        <v>150000</v>
+      </c>
+      <c r="Q25" s="27">
+        <v>158000</v>
+      </c>
+      <c r="R25" s="26">
+        <v>139000</v>
+      </c>
+      <c r="S25" s="27">
+        <v>41500</v>
       </c>
       <c r="T25" s="16">
         <v>120</v>
@@ -2829,23 +2846,23 @@
         <v>9200</v>
       </c>
       <c r="J26" s="19"/>
-      <c r="N26" s="22">
-        <v>328000</v>
-      </c>
-      <c r="O26" s="22">
-        <v>328000</v>
-      </c>
-      <c r="P26" s="22">
-        <v>217000</v>
-      </c>
-      <c r="Q26" s="22">
-        <v>217000</v>
-      </c>
-      <c r="R26" s="13">
-        <v>210000</v>
-      </c>
-      <c r="S26" s="18">
-        <v>45000</v>
+      <c r="N26" s="25">
+        <v>220000</v>
+      </c>
+      <c r="O26" s="26">
+        <v>231000</v>
+      </c>
+      <c r="P26" s="27">
+        <v>158000</v>
+      </c>
+      <c r="Q26" s="27">
+        <v>166000</v>
+      </c>
+      <c r="R26" s="26">
+        <v>146000</v>
+      </c>
+      <c r="S26" s="27">
+        <v>43500</v>
       </c>
       <c r="T26" s="16">
         <v>125</v>
@@ -2874,23 +2891,23 @@
       <c r="H27" s="20">
         <v>9600</v>
       </c>
-      <c r="N27" s="22">
-        <v>346000</v>
-      </c>
-      <c r="O27" s="22">
-        <v>346000</v>
-      </c>
-      <c r="P27" s="22">
-        <v>229000</v>
-      </c>
-      <c r="Q27" s="22">
-        <v>229000</v>
-      </c>
-      <c r="R27" s="13">
-        <v>220000</v>
-      </c>
-      <c r="S27" s="18">
-        <v>47000</v>
+      <c r="N27" s="25">
+        <v>231000</v>
+      </c>
+      <c r="O27" s="26">
+        <v>242000</v>
+      </c>
+      <c r="P27" s="27">
+        <v>166000</v>
+      </c>
+      <c r="Q27" s="27">
+        <v>174000</v>
+      </c>
+      <c r="R27" s="26">
+        <v>153000</v>
+      </c>
+      <c r="S27" s="27">
+        <v>45500</v>
       </c>
       <c r="T27" s="16">
         <v>130</v>
@@ -2919,23 +2936,23 @@
       <c r="H28" s="20">
         <v>10000</v>
       </c>
-      <c r="N28" s="22">
-        <v>364000</v>
-      </c>
-      <c r="O28" s="22">
-        <v>364000</v>
-      </c>
-      <c r="P28" s="22">
-        <v>241000</v>
-      </c>
-      <c r="Q28" s="22">
-        <v>241000</v>
-      </c>
-      <c r="R28" s="13">
-        <v>230000</v>
-      </c>
-      <c r="S28" s="18">
-        <v>49000</v>
+      <c r="N28" s="25">
+        <v>242000</v>
+      </c>
+      <c r="O28" s="26">
+        <v>253000</v>
+      </c>
+      <c r="P28" s="27">
+        <v>174000</v>
+      </c>
+      <c r="Q28" s="27">
+        <v>182000</v>
+      </c>
+      <c r="R28" s="26">
+        <v>160000</v>
+      </c>
+      <c r="S28" s="27">
+        <v>47500</v>
       </c>
       <c r="T28" s="16">
         <v>135</v>
@@ -2964,23 +2981,23 @@
       <c r="H29" s="20">
         <v>10400</v>
       </c>
-      <c r="N29" s="22">
-        <v>382000</v>
-      </c>
-      <c r="O29" s="22">
-        <v>382000</v>
-      </c>
-      <c r="P29" s="22">
+      <c r="N29" s="25">
         <v>253000</v>
       </c>
-      <c r="Q29" s="22">
-        <v>253000</v>
-      </c>
-      <c r="R29" s="13">
-        <v>240000</v>
-      </c>
-      <c r="S29" s="18">
-        <v>51000</v>
+      <c r="O29" s="26">
+        <v>264000</v>
+      </c>
+      <c r="P29" s="27">
+        <v>182000</v>
+      </c>
+      <c r="Q29" s="27">
+        <v>190000</v>
+      </c>
+      <c r="R29" s="26">
+        <v>167000</v>
+      </c>
+      <c r="S29" s="27">
+        <v>49500</v>
       </c>
       <c r="T29" s="16">
         <v>140</v>
@@ -3009,23 +3026,23 @@
       <c r="H30" s="20">
         <v>10800</v>
       </c>
-      <c r="N30" s="22">
-        <v>400000</v>
-      </c>
-      <c r="O30" s="22">
-        <v>400000</v>
-      </c>
-      <c r="P30" s="22">
-        <v>265000</v>
-      </c>
-      <c r="Q30" s="22">
-        <v>265000</v>
-      </c>
-      <c r="R30" s="13">
-        <v>250000</v>
-      </c>
-      <c r="S30" s="18">
-        <v>53000</v>
+      <c r="N30" s="25">
+        <v>264000</v>
+      </c>
+      <c r="O30" s="26">
+        <v>275000</v>
+      </c>
+      <c r="P30" s="27">
+        <v>190000</v>
+      </c>
+      <c r="Q30" s="27">
+        <v>198000</v>
+      </c>
+      <c r="R30" s="26">
+        <v>174000</v>
+      </c>
+      <c r="S30" s="27">
+        <v>51500</v>
       </c>
       <c r="T30" s="16">
         <v>145</v>
@@ -3054,23 +3071,23 @@
       <c r="H31" s="20">
         <v>11200</v>
       </c>
-      <c r="N31" s="22">
-        <v>418000</v>
-      </c>
-      <c r="O31" s="22">
-        <v>418000</v>
-      </c>
-      <c r="P31" s="22">
-        <v>277000</v>
-      </c>
-      <c r="Q31" s="22">
-        <v>277000</v>
-      </c>
-      <c r="R31" s="13">
-        <v>260000</v>
-      </c>
-      <c r="S31" s="18">
-        <v>55000</v>
+      <c r="N31" s="25">
+        <v>275000</v>
+      </c>
+      <c r="O31" s="26">
+        <v>286000</v>
+      </c>
+      <c r="P31" s="27">
+        <v>198000</v>
+      </c>
+      <c r="Q31" s="27">
+        <v>206000</v>
+      </c>
+      <c r="R31" s="26">
+        <v>181000</v>
+      </c>
+      <c r="S31" s="27">
+        <v>53500</v>
       </c>
       <c r="T31" s="16">
         <v>150</v>
@@ -3099,23 +3116,23 @@
       <c r="H32" s="20">
         <v>11600</v>
       </c>
-      <c r="N32" s="22">
-        <v>436000</v>
-      </c>
-      <c r="O32" s="22">
-        <v>436000</v>
-      </c>
-      <c r="P32" s="22">
-        <v>289000</v>
-      </c>
-      <c r="Q32" s="22">
-        <v>289000</v>
-      </c>
-      <c r="R32" s="13">
-        <v>270000</v>
-      </c>
-      <c r="S32" s="18">
-        <v>57000</v>
+      <c r="N32" s="25">
+        <v>286000</v>
+      </c>
+      <c r="O32" s="26">
+        <v>297000</v>
+      </c>
+      <c r="P32" s="27">
+        <v>206000</v>
+      </c>
+      <c r="Q32" s="27">
+        <v>214000</v>
+      </c>
+      <c r="R32" s="26">
+        <v>188000</v>
+      </c>
+      <c r="S32" s="27">
+        <v>55500</v>
       </c>
       <c r="T32" s="16">
         <v>155</v>
@@ -3131,21 +3148,11 @@
       <c r="H33" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="N33" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="O33" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="P33" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q33" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="R33" s="23" t="s">
-        <v>90</v>
-      </c>
+      <c r="N33" s="28"/>
+      <c r="O33" s="28"/>
+      <c r="P33" s="28"/>
+      <c r="Q33" s="28"/>
+      <c r="R33" s="28"/>
       <c r="U33" s="23" t="s">
         <v>86</v>
       </c>

--- a/돌발 노출 조건 정리.xlsx
+++ b/돌발 노출 조건 정리.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dksru\Desktop\NanseExcel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\투캉 공유 폴더\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA2A76A-C5B0-4B15-9899-D13245E0D743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED4607D-7C7C-4817-AD55-FF740A428166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{03183270-ED35-4CBA-B934-C51A3B93B442}"/>
+    <workbookView xWindow="44130" yWindow="2475" windowWidth="23070" windowHeight="15480" activeTab="1" xr2:uid="{03183270-ED35-4CBA-B934-C51A3B93B442}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="테스트" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="116">
   <si>
     <r>
       <t>도철</t>
@@ -682,6 +683,114 @@
   </si>
   <si>
     <t>임의조정함</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>표류자[41스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1250[30스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3000[30스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>60[61스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2000[72스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4000[84스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5[86스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>11[86스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>10[86스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>90[91스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>무사[100스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>100[100스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>300[100스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>120[120스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3000[139스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>150[150스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>검객[157스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>7000[169스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>180[180스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>12000[182스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>17[182스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>30[182스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000[183스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000[200스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>200[200스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>투사[206스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>8000[206스테]</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -882,7 +991,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -968,6 +1077,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="계산" xfId="3" builtinId="22"/>
@@ -3161,4 +3294,1909 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1605EDAA-0894-4BA7-9489-739EB1E4A614}">
+  <dimension ref="A1:W33"/>
+  <sheetFormatPr defaultColWidth="3.375" defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="5.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.875" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.875" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="19" width="14.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.75" style="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14" style="8" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.25" style="8" customWidth="1"/>
+    <col min="25" max="25" width="4" style="8" customWidth="1"/>
+    <col min="26" max="27" width="3.375" style="8"/>
+    <col min="28" max="28" width="4.5" style="8" customWidth="1"/>
+    <col min="29" max="16384" width="3.375" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" s="5" customFormat="1">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="S1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="T1" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="U1" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="V1" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="W1" s="12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" s="6" customFormat="1">
+      <c r="A2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="S2" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23">
+      <c r="A3" s="7">
+        <v>1</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="33">
+        <v>35</v>
+      </c>
+      <c r="E3" s="29">
+        <v>50</v>
+      </c>
+      <c r="F3" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="H3" s="35">
+        <v>200</v>
+      </c>
+      <c r="I3" s="29">
+        <v>1</v>
+      </c>
+      <c r="J3" s="29">
+        <v>1000</v>
+      </c>
+      <c r="K3" s="29">
+        <v>1</v>
+      </c>
+      <c r="L3" s="29">
+        <v>1000</v>
+      </c>
+      <c r="M3" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="N3" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="O3" s="31">
+        <v>4000</v>
+      </c>
+      <c r="P3" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q3" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="R3" s="31">
+        <v>300</v>
+      </c>
+      <c r="S3" s="32">
+        <v>200</v>
+      </c>
+      <c r="T3" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="U3" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="V3" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="W3" s="33" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
+      <c r="A4" s="7">
+        <v>2</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="33">
+        <v>85</v>
+      </c>
+      <c r="E4" s="29">
+        <v>100</v>
+      </c>
+      <c r="F4" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="H4" s="35">
+        <v>400</v>
+      </c>
+      <c r="I4" s="29">
+        <v>100</v>
+      </c>
+      <c r="J4" s="29">
+        <v>2000</v>
+      </c>
+      <c r="K4" s="29">
+        <v>100</v>
+      </c>
+      <c r="L4" s="29">
+        <v>2000</v>
+      </c>
+      <c r="M4" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="N4" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="O4" s="31">
+        <v>7000</v>
+      </c>
+      <c r="P4" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q4" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="R4" s="31">
+        <v>2000</v>
+      </c>
+      <c r="S4" s="32">
+        <v>1000</v>
+      </c>
+      <c r="T4" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="U4" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="V4" s="29">
+        <v>20</v>
+      </c>
+      <c r="W4" s="33" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
+      <c r="A5" s="7">
+        <v>3</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" s="33">
+        <v>135</v>
+      </c>
+      <c r="E5" s="29">
+        <v>150</v>
+      </c>
+      <c r="F5" s="32">
+        <v>4000</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="H5" s="35">
+        <v>800</v>
+      </c>
+      <c r="I5" s="29">
+        <v>200</v>
+      </c>
+      <c r="J5" s="29">
+        <v>3000</v>
+      </c>
+      <c r="K5" s="29">
+        <v>200</v>
+      </c>
+      <c r="L5" s="29">
+        <v>3000</v>
+      </c>
+      <c r="M5" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="N5" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="O5" s="31">
+        <v>12000</v>
+      </c>
+      <c r="P5" s="32">
+        <v>5000</v>
+      </c>
+      <c r="Q5" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="R5" s="31">
+        <v>4000</v>
+      </c>
+      <c r="S5" s="32">
+        <v>2000</v>
+      </c>
+      <c r="T5" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="U5" s="29">
+        <v>50</v>
+      </c>
+      <c r="V5" s="29">
+        <v>35</v>
+      </c>
+      <c r="W5" s="33" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23">
+      <c r="A6" s="7">
+        <v>4</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="29">
+        <v>250</v>
+      </c>
+      <c r="D6" s="33">
+        <v>185</v>
+      </c>
+      <c r="E6" s="29">
+        <v>200</v>
+      </c>
+      <c r="F6" s="32">
+        <v>8000</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="H6" s="35">
+        <v>1200</v>
+      </c>
+      <c r="I6" s="29">
+        <v>300</v>
+      </c>
+      <c r="J6" s="29">
+        <v>4000</v>
+      </c>
+      <c r="K6" s="29">
+        <v>300</v>
+      </c>
+      <c r="L6" s="29">
+        <v>4000</v>
+      </c>
+      <c r="M6" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="N6" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="O6" s="31">
+        <v>17000</v>
+      </c>
+      <c r="P6" s="32">
+        <v>8000</v>
+      </c>
+      <c r="Q6" s="32">
+        <v>11000</v>
+      </c>
+      <c r="R6" s="31">
+        <v>6000</v>
+      </c>
+      <c r="S6" s="32">
+        <v>3500</v>
+      </c>
+      <c r="T6" s="29">
+        <v>23</v>
+      </c>
+      <c r="U6" s="29">
+        <v>70</v>
+      </c>
+      <c r="V6" s="29">
+        <v>50</v>
+      </c>
+      <c r="W6" s="33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23">
+      <c r="A7" s="7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="29">
+        <v>240</v>
+      </c>
+      <c r="C7" s="29">
+        <v>300</v>
+      </c>
+      <c r="D7" s="33">
+        <v>235</v>
+      </c>
+      <c r="E7" s="29">
+        <v>250</v>
+      </c>
+      <c r="F7" s="32">
+        <v>12000</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="35">
+        <v>1600</v>
+      </c>
+      <c r="I7" s="29">
+        <v>400</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="K7" s="29">
+        <v>400</v>
+      </c>
+      <c r="L7" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="M7" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="30">
+        <v>17000</v>
+      </c>
+      <c r="O7" s="31">
+        <v>22000</v>
+      </c>
+      <c r="P7" s="32">
+        <v>11000</v>
+      </c>
+      <c r="Q7" s="32">
+        <v>14000</v>
+      </c>
+      <c r="R7" s="31">
+        <v>13000</v>
+      </c>
+      <c r="S7" s="32">
+        <v>5500</v>
+      </c>
+      <c r="T7" s="29">
+        <v>29</v>
+      </c>
+      <c r="U7" s="29">
+        <v>90</v>
+      </c>
+      <c r="V7" s="29">
+        <v>65</v>
+      </c>
+      <c r="W7" s="33" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23">
+      <c r="A8" s="7">
+        <v>6</v>
+      </c>
+      <c r="B8" s="29">
+        <v>315</v>
+      </c>
+      <c r="C8" s="29">
+        <v>350</v>
+      </c>
+      <c r="D8" s="33">
+        <v>285</v>
+      </c>
+      <c r="E8" s="29">
+        <v>300</v>
+      </c>
+      <c r="F8" s="32">
+        <v>16000</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="35">
+        <v>2000</v>
+      </c>
+      <c r="I8" s="29">
+        <v>500</v>
+      </c>
+      <c r="J8"/>
+      <c r="K8" s="29">
+        <v>500</v>
+      </c>
+      <c r="L8"/>
+      <c r="M8" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="N8" s="30">
+        <v>22000</v>
+      </c>
+      <c r="O8" s="31">
+        <v>33000</v>
+      </c>
+      <c r="P8" s="32">
+        <v>14000</v>
+      </c>
+      <c r="Q8" s="32">
+        <v>22000</v>
+      </c>
+      <c r="R8" s="31">
+        <v>20000</v>
+      </c>
+      <c r="S8" s="32">
+        <v>7500</v>
+      </c>
+      <c r="T8" s="29">
+        <v>35</v>
+      </c>
+      <c r="U8" s="29">
+        <v>110</v>
+      </c>
+      <c r="V8" s="29">
+        <v>80</v>
+      </c>
+      <c r="W8" s="33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
+      <c r="A9" s="7">
+        <v>7</v>
+      </c>
+      <c r="B9" s="29">
+        <v>375</v>
+      </c>
+      <c r="C9" s="29">
+        <v>400</v>
+      </c>
+      <c r="D9" s="33">
+        <v>335</v>
+      </c>
+      <c r="E9" s="29">
+        <v>350</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="35">
+        <v>2400</v>
+      </c>
+      <c r="I9" s="29">
+        <v>600</v>
+      </c>
+      <c r="J9"/>
+      <c r="K9" s="29">
+        <v>600</v>
+      </c>
+      <c r="L9"/>
+      <c r="M9" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="N9" s="30">
+        <v>33000</v>
+      </c>
+      <c r="O9" s="31">
+        <v>44000</v>
+      </c>
+      <c r="P9" s="32">
+        <v>22000</v>
+      </c>
+      <c r="Q9" s="32">
+        <v>30000</v>
+      </c>
+      <c r="R9" s="31">
+        <v>27000</v>
+      </c>
+      <c r="S9" s="32">
+        <v>9500</v>
+      </c>
+      <c r="T9" s="29">
+        <v>40</v>
+      </c>
+      <c r="U9" s="29">
+        <v>130</v>
+      </c>
+      <c r="V9" s="29">
+        <v>95</v>
+      </c>
+      <c r="W9" s="33" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23">
+      <c r="A10" s="7">
+        <v>8</v>
+      </c>
+      <c r="B10" s="29">
+        <v>435</v>
+      </c>
+      <c r="C10" s="29">
+        <v>450</v>
+      </c>
+      <c r="D10" s="33">
+        <v>385</v>
+      </c>
+      <c r="E10" s="29">
+        <v>400</v>
+      </c>
+      <c r="F10" s="30">
+        <v>300</v>
+      </c>
+      <c r="G10" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" s="35">
+        <v>2800</v>
+      </c>
+      <c r="I10" s="29">
+        <v>700</v>
+      </c>
+      <c r="J10"/>
+      <c r="K10" s="29">
+        <v>700</v>
+      </c>
+      <c r="L10"/>
+      <c r="M10" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="30">
+        <v>44000</v>
+      </c>
+      <c r="O10" s="31">
+        <v>55000</v>
+      </c>
+      <c r="P10" s="32">
+        <v>30000</v>
+      </c>
+      <c r="Q10" s="32">
+        <v>38000</v>
+      </c>
+      <c r="R10" s="31">
+        <v>34000</v>
+      </c>
+      <c r="S10" s="32">
+        <v>11500</v>
+      </c>
+      <c r="T10" s="29">
+        <v>45</v>
+      </c>
+      <c r="U10" s="29">
+        <v>150</v>
+      </c>
+      <c r="V10" s="29">
+        <v>110</v>
+      </c>
+      <c r="W10" s="33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23">
+      <c r="A11" s="7">
+        <v>9</v>
+      </c>
+      <c r="B11" s="29">
+        <v>495</v>
+      </c>
+      <c r="C11" s="29">
+        <v>500</v>
+      </c>
+      <c r="D11" s="33">
+        <v>435</v>
+      </c>
+      <c r="E11" s="29">
+        <v>450</v>
+      </c>
+      <c r="F11" s="30">
+        <v>1000</v>
+      </c>
+      <c r="G11" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="35">
+        <v>3200</v>
+      </c>
+      <c r="I11" s="29">
+        <v>800</v>
+      </c>
+      <c r="J11"/>
+      <c r="K11" s="29">
+        <v>800</v>
+      </c>
+      <c r="L11"/>
+      <c r="M11" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="N11" s="30">
+        <v>55000</v>
+      </c>
+      <c r="O11" s="31">
+        <v>66000</v>
+      </c>
+      <c r="P11" s="32">
+        <v>38000</v>
+      </c>
+      <c r="Q11" s="32">
+        <v>46000</v>
+      </c>
+      <c r="R11" s="31">
+        <v>41000</v>
+      </c>
+      <c r="S11" s="32">
+        <v>13500</v>
+      </c>
+      <c r="T11" s="29">
+        <v>50</v>
+      </c>
+      <c r="U11" s="29">
+        <v>170</v>
+      </c>
+      <c r="V11" s="29">
+        <v>125</v>
+      </c>
+      <c r="W11" s="33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
+      <c r="A12" s="7">
+        <v>10</v>
+      </c>
+      <c r="B12" s="29">
+        <v>575</v>
+      </c>
+      <c r="C12" s="29">
+        <v>550</v>
+      </c>
+      <c r="D12" s="33">
+        <v>485</v>
+      </c>
+      <c r="E12" s="29">
+        <v>500</v>
+      </c>
+      <c r="F12" s="30">
+        <v>4000</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" s="35">
+        <v>3600</v>
+      </c>
+      <c r="I12" s="29">
+        <v>900</v>
+      </c>
+      <c r="J12"/>
+      <c r="K12" s="29">
+        <v>900</v>
+      </c>
+      <c r="L12"/>
+      <c r="M12" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="30">
+        <v>66000</v>
+      </c>
+      <c r="O12" s="31">
+        <v>77000</v>
+      </c>
+      <c r="P12" s="32">
+        <v>46000</v>
+      </c>
+      <c r="Q12" s="32">
+        <v>54000</v>
+      </c>
+      <c r="R12" s="31">
+        <v>48000</v>
+      </c>
+      <c r="S12" s="32">
+        <v>15500</v>
+      </c>
+      <c r="T12" s="29">
+        <v>55</v>
+      </c>
+      <c r="U12" s="29">
+        <v>190</v>
+      </c>
+      <c r="V12" s="29">
+        <v>140</v>
+      </c>
+      <c r="W12" s="33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
+      <c r="A13" s="7">
+        <v>11</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="29">
+        <v>600</v>
+      </c>
+      <c r="D13" s="33">
+        <v>535</v>
+      </c>
+      <c r="E13" s="29">
+        <v>550</v>
+      </c>
+      <c r="F13" s="30">
+        <v>6000</v>
+      </c>
+      <c r="G13" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" s="35">
+        <v>4000</v>
+      </c>
+      <c r="I13" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="J13"/>
+      <c r="K13" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="L13"/>
+      <c r="M13" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="N13" s="30">
+        <v>77000</v>
+      </c>
+      <c r="O13" s="31">
+        <v>88000</v>
+      </c>
+      <c r="P13" s="32">
+        <v>54000</v>
+      </c>
+      <c r="Q13" s="32">
+        <v>62000</v>
+      </c>
+      <c r="R13" s="31">
+        <v>55000</v>
+      </c>
+      <c r="S13" s="32">
+        <v>17500</v>
+      </c>
+      <c r="T13" s="29">
+        <v>60</v>
+      </c>
+      <c r="U13" s="29">
+        <v>210</v>
+      </c>
+      <c r="V13" s="29">
+        <v>155</v>
+      </c>
+      <c r="W13" s="33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
+      <c r="A14" s="7">
+        <v>12</v>
+      </c>
+      <c r="C14" s="29">
+        <v>650</v>
+      </c>
+      <c r="D14" s="33">
+        <v>585</v>
+      </c>
+      <c r="E14" s="29">
+        <v>600</v>
+      </c>
+      <c r="F14" s="30">
+        <v>8000</v>
+      </c>
+      <c r="H14" s="35">
+        <v>4400</v>
+      </c>
+      <c r="J14"/>
+      <c r="L14"/>
+      <c r="M14" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="N14" s="30">
+        <v>88000</v>
+      </c>
+      <c r="O14" s="31">
+        <v>99000</v>
+      </c>
+      <c r="P14" s="32">
+        <v>62000</v>
+      </c>
+      <c r="Q14" s="32">
+        <v>70000</v>
+      </c>
+      <c r="R14" s="31">
+        <v>62000</v>
+      </c>
+      <c r="S14" s="32">
+        <v>19500</v>
+      </c>
+      <c r="T14" s="29">
+        <v>65</v>
+      </c>
+      <c r="U14" s="29">
+        <v>230</v>
+      </c>
+      <c r="V14" s="29">
+        <v>170</v>
+      </c>
+      <c r="W14" s="33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23">
+      <c r="A15" s="7">
+        <v>13</v>
+      </c>
+      <c r="C15" s="29">
+        <v>700</v>
+      </c>
+      <c r="D15" s="33">
+        <v>635</v>
+      </c>
+      <c r="E15" s="29">
+        <v>650</v>
+      </c>
+      <c r="F15" s="30">
+        <v>10000</v>
+      </c>
+      <c r="H15" s="35">
+        <v>4800</v>
+      </c>
+      <c r="J15"/>
+      <c r="L15"/>
+      <c r="M15" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="N15" s="30">
+        <v>99000</v>
+      </c>
+      <c r="O15" s="31">
+        <v>110000</v>
+      </c>
+      <c r="P15" s="32">
+        <v>70000</v>
+      </c>
+      <c r="Q15" s="32">
+        <v>78000</v>
+      </c>
+      <c r="R15" s="31">
+        <v>69000</v>
+      </c>
+      <c r="S15" s="32">
+        <v>21500</v>
+      </c>
+      <c r="T15" s="29">
+        <v>70</v>
+      </c>
+      <c r="U15" s="29">
+        <v>250</v>
+      </c>
+      <c r="V15" s="29">
+        <v>185</v>
+      </c>
+      <c r="W15" s="33" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23">
+      <c r="A16" s="7">
+        <v>14</v>
+      </c>
+      <c r="C16" s="29">
+        <v>750</v>
+      </c>
+      <c r="D16" s="33">
+        <v>685</v>
+      </c>
+      <c r="E16" s="29">
+        <v>700</v>
+      </c>
+      <c r="F16" s="30">
+        <v>12000</v>
+      </c>
+      <c r="H16" s="35">
+        <v>5200</v>
+      </c>
+      <c r="J16"/>
+      <c r="L16"/>
+      <c r="M16" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="N16" s="30">
+        <v>110000</v>
+      </c>
+      <c r="O16" s="31">
+        <v>121000</v>
+      </c>
+      <c r="P16" s="32">
+        <v>78000</v>
+      </c>
+      <c r="Q16" s="32">
+        <v>86000</v>
+      </c>
+      <c r="R16" s="31">
+        <v>76000</v>
+      </c>
+      <c r="S16" s="32">
+        <v>23500</v>
+      </c>
+      <c r="T16" s="29">
+        <v>75</v>
+      </c>
+      <c r="U16" s="29">
+        <v>270</v>
+      </c>
+      <c r="V16" s="29">
+        <v>200</v>
+      </c>
+      <c r="W16" s="33" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23">
+      <c r="A17" s="7">
+        <v>15</v>
+      </c>
+      <c r="C17" s="29">
+        <v>800</v>
+      </c>
+      <c r="D17" s="33">
+        <v>735</v>
+      </c>
+      <c r="E17" s="29">
+        <v>750</v>
+      </c>
+      <c r="F17" s="30">
+        <v>14000</v>
+      </c>
+      <c r="H17" s="35">
+        <v>5600</v>
+      </c>
+      <c r="J17"/>
+      <c r="L17"/>
+      <c r="M17" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="N17" s="30">
+        <v>121000</v>
+      </c>
+      <c r="O17" s="31">
+        <v>132000</v>
+      </c>
+      <c r="P17" s="32">
+        <v>86000</v>
+      </c>
+      <c r="Q17" s="32">
+        <v>94000</v>
+      </c>
+      <c r="R17" s="31">
+        <v>83000</v>
+      </c>
+      <c r="S17" s="32">
+        <v>25500</v>
+      </c>
+      <c r="T17" s="29">
+        <v>80</v>
+      </c>
+      <c r="U17" s="29">
+        <v>290</v>
+      </c>
+      <c r="V17" s="29">
+        <v>215</v>
+      </c>
+      <c r="W17" s="33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23">
+      <c r="A18" s="7">
+        <v>16</v>
+      </c>
+      <c r="C18" s="29">
+        <v>850</v>
+      </c>
+      <c r="D18" s="33">
+        <v>785</v>
+      </c>
+      <c r="E18" s="29">
+        <v>800</v>
+      </c>
+      <c r="F18" s="30">
+        <v>16000</v>
+      </c>
+      <c r="H18" s="35">
+        <v>6000</v>
+      </c>
+      <c r="J18"/>
+      <c r="L18"/>
+      <c r="M18" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="N18" s="30">
+        <v>132000</v>
+      </c>
+      <c r="O18" s="31">
+        <v>143000</v>
+      </c>
+      <c r="P18" s="32">
+        <v>94000</v>
+      </c>
+      <c r="Q18" s="32">
+        <v>102000</v>
+      </c>
+      <c r="R18" s="31">
+        <v>90000</v>
+      </c>
+      <c r="S18" s="32">
+        <v>27500</v>
+      </c>
+      <c r="T18" s="29">
+        <v>85</v>
+      </c>
+      <c r="U18" s="29">
+        <v>310</v>
+      </c>
+      <c r="V18" s="29">
+        <v>230</v>
+      </c>
+      <c r="W18" s="33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23">
+      <c r="A19" s="7">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="29">
+        <v>900</v>
+      </c>
+      <c r="D19" s="33">
+        <v>835</v>
+      </c>
+      <c r="E19" s="29">
+        <v>850</v>
+      </c>
+      <c r="F19" s="30">
+        <v>18000</v>
+      </c>
+      <c r="H19" s="35">
+        <v>6400</v>
+      </c>
+      <c r="J19"/>
+      <c r="L19"/>
+      <c r="M19" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="N19" s="30">
+        <v>143000</v>
+      </c>
+      <c r="O19" s="31">
+        <v>154000</v>
+      </c>
+      <c r="P19" s="32">
+        <v>102000</v>
+      </c>
+      <c r="Q19" s="32">
+        <v>110000</v>
+      </c>
+      <c r="R19" s="31">
+        <v>97000</v>
+      </c>
+      <c r="S19" s="32">
+        <v>29500</v>
+      </c>
+      <c r="T19" s="29">
+        <v>90</v>
+      </c>
+      <c r="U19" s="29">
+        <v>330</v>
+      </c>
+      <c r="V19" s="29">
+        <v>245</v>
+      </c>
+      <c r="W19" s="29"/>
+    </row>
+    <row r="20" spans="1:23">
+      <c r="A20" s="7">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="29">
+        <v>950</v>
+      </c>
+      <c r="D20" s="33">
+        <v>885</v>
+      </c>
+      <c r="E20" s="29">
+        <v>900</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="H20" s="35">
+        <v>6800</v>
+      </c>
+      <c r="J20"/>
+      <c r="K20"/>
+      <c r="L20"/>
+      <c r="M20" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="N20" s="30">
+        <v>154000</v>
+      </c>
+      <c r="O20" s="31">
+        <v>165000</v>
+      </c>
+      <c r="P20" s="32">
+        <v>110000</v>
+      </c>
+      <c r="Q20" s="32">
+        <v>118000</v>
+      </c>
+      <c r="R20" s="31">
+        <v>104000</v>
+      </c>
+      <c r="S20" s="32">
+        <v>31500</v>
+      </c>
+      <c r="T20" s="29">
+        <v>95</v>
+      </c>
+      <c r="U20" s="29">
+        <v>350</v>
+      </c>
+      <c r="V20" s="29">
+        <v>260</v>
+      </c>
+      <c r="W20" s="29"/>
+    </row>
+    <row r="21" spans="1:23">
+      <c r="A21" s="7">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="29">
+        <v>1000</v>
+      </c>
+      <c r="D21" s="33">
+        <v>935</v>
+      </c>
+      <c r="E21" s="29">
+        <v>950</v>
+      </c>
+      <c r="F21"/>
+      <c r="H21" s="35">
+        <v>7200</v>
+      </c>
+      <c r="J21"/>
+      <c r="K21"/>
+      <c r="L21"/>
+      <c r="M21" s="29"/>
+      <c r="N21" s="30">
+        <v>165000</v>
+      </c>
+      <c r="O21" s="31">
+        <v>176000</v>
+      </c>
+      <c r="P21" s="32">
+        <v>118000</v>
+      </c>
+      <c r="Q21" s="32">
+        <v>126000</v>
+      </c>
+      <c r="R21" s="31">
+        <v>111000</v>
+      </c>
+      <c r="S21" s="32">
+        <v>33500</v>
+      </c>
+      <c r="T21" s="29">
+        <v>100</v>
+      </c>
+      <c r="U21" s="29">
+        <v>370</v>
+      </c>
+      <c r="V21" s="29">
+        <v>275</v>
+      </c>
+      <c r="W21" s="29"/>
+    </row>
+    <row r="22" spans="1:23">
+      <c r="A22" s="7">
+        <v>20</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="29">
+        <v>1050</v>
+      </c>
+      <c r="D22" s="33">
+        <v>985</v>
+      </c>
+      <c r="E22" s="29">
+        <v>1000</v>
+      </c>
+      <c r="F22"/>
+      <c r="H22" s="35">
+        <v>7600</v>
+      </c>
+      <c r="J22"/>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="M22" s="29"/>
+      <c r="N22" s="30">
+        <v>176000</v>
+      </c>
+      <c r="O22" s="31">
+        <v>187000</v>
+      </c>
+      <c r="P22" s="32">
+        <v>126000</v>
+      </c>
+      <c r="Q22" s="32">
+        <v>134000</v>
+      </c>
+      <c r="R22" s="31">
+        <v>118000</v>
+      </c>
+      <c r="S22" s="32">
+        <v>35500</v>
+      </c>
+      <c r="T22" s="29">
+        <v>105</v>
+      </c>
+      <c r="U22" s="29">
+        <v>390</v>
+      </c>
+      <c r="V22" s="29">
+        <v>290</v>
+      </c>
+      <c r="W22" s="30"/>
+    </row>
+    <row r="23" spans="1:23">
+      <c r="A23" s="7">
+        <v>21</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="29">
+        <v>1100</v>
+      </c>
+      <c r="D23" s="33">
+        <v>1035</v>
+      </c>
+      <c r="E23" s="29">
+        <v>1050</v>
+      </c>
+      <c r="F23"/>
+      <c r="H23" s="35">
+        <v>8000</v>
+      </c>
+      <c r="M23" s="29"/>
+      <c r="N23" s="30">
+        <v>187000</v>
+      </c>
+      <c r="O23" s="31">
+        <v>198000</v>
+      </c>
+      <c r="P23" s="32">
+        <v>134000</v>
+      </c>
+      <c r="Q23" s="32">
+        <v>142000</v>
+      </c>
+      <c r="R23" s="31">
+        <v>125000</v>
+      </c>
+      <c r="S23" s="32">
+        <v>37500</v>
+      </c>
+      <c r="T23" s="29">
+        <v>110</v>
+      </c>
+      <c r="U23" s="29">
+        <v>410</v>
+      </c>
+      <c r="V23" s="29">
+        <v>305</v>
+      </c>
+      <c r="W23" s="29"/>
+    </row>
+    <row r="24" spans="1:23">
+      <c r="A24" s="7">
+        <v>22</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="29">
+        <v>1150</v>
+      </c>
+      <c r="D24" s="33">
+        <v>1085</v>
+      </c>
+      <c r="E24" s="29">
+        <v>1100</v>
+      </c>
+      <c r="H24" s="35">
+        <v>8400</v>
+      </c>
+      <c r="J24" s="19"/>
+      <c r="M24" s="29"/>
+      <c r="N24" s="30">
+        <v>198000</v>
+      </c>
+      <c r="O24" s="31">
+        <v>209000</v>
+      </c>
+      <c r="P24" s="32">
+        <v>142000</v>
+      </c>
+      <c r="Q24" s="32">
+        <v>150000</v>
+      </c>
+      <c r="R24" s="31">
+        <v>132000</v>
+      </c>
+      <c r="S24" s="32">
+        <v>39500</v>
+      </c>
+      <c r="T24" s="29">
+        <v>115</v>
+      </c>
+      <c r="U24" s="29">
+        <v>430</v>
+      </c>
+      <c r="V24" s="29">
+        <v>320</v>
+      </c>
+      <c r="W24" s="29"/>
+    </row>
+    <row r="25" spans="1:23">
+      <c r="A25" s="7">
+        <v>23</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="29">
+        <v>1200</v>
+      </c>
+      <c r="D25" s="33">
+        <v>1135</v>
+      </c>
+      <c r="E25" s="29">
+        <v>1150</v>
+      </c>
+      <c r="H25" s="35">
+        <v>8800</v>
+      </c>
+      <c r="M25" s="29"/>
+      <c r="N25" s="30">
+        <v>209000</v>
+      </c>
+      <c r="O25" s="31">
+        <v>220000</v>
+      </c>
+      <c r="P25" s="32">
+        <v>150000</v>
+      </c>
+      <c r="Q25" s="32">
+        <v>158000</v>
+      </c>
+      <c r="R25" s="31">
+        <v>139000</v>
+      </c>
+      <c r="S25" s="32">
+        <v>41500</v>
+      </c>
+      <c r="T25" s="29">
+        <v>120</v>
+      </c>
+      <c r="U25" s="29">
+        <v>450</v>
+      </c>
+      <c r="V25" s="29">
+        <v>335</v>
+      </c>
+      <c r="W25" s="29"/>
+    </row>
+    <row r="26" spans="1:23">
+      <c r="A26" s="7">
+        <v>24</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="29">
+        <v>1250</v>
+      </c>
+      <c r="D26" s="33">
+        <v>1185</v>
+      </c>
+      <c r="E26" s="29">
+        <v>1200</v>
+      </c>
+      <c r="H26" s="35">
+        <v>9200</v>
+      </c>
+      <c r="J26" s="19"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="30">
+        <v>220000</v>
+      </c>
+      <c r="O26" s="31">
+        <v>231000</v>
+      </c>
+      <c r="P26" s="32">
+        <v>158000</v>
+      </c>
+      <c r="Q26" s="32">
+        <v>166000</v>
+      </c>
+      <c r="R26" s="31">
+        <v>146000</v>
+      </c>
+      <c r="S26" s="32">
+        <v>43500</v>
+      </c>
+      <c r="T26" s="29">
+        <v>125</v>
+      </c>
+      <c r="U26" s="29">
+        <v>470</v>
+      </c>
+      <c r="V26" s="29">
+        <v>350</v>
+      </c>
+      <c r="W26" s="29"/>
+    </row>
+    <row r="27" spans="1:23">
+      <c r="A27" s="7">
+        <v>25</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="29">
+        <v>1300</v>
+      </c>
+      <c r="D27" s="33">
+        <v>1235</v>
+      </c>
+      <c r="E27" s="29">
+        <v>1250</v>
+      </c>
+      <c r="H27" s="35">
+        <v>9600</v>
+      </c>
+      <c r="M27" s="29"/>
+      <c r="N27" s="30">
+        <v>231000</v>
+      </c>
+      <c r="O27" s="31">
+        <v>242000</v>
+      </c>
+      <c r="P27" s="32">
+        <v>166000</v>
+      </c>
+      <c r="Q27" s="32">
+        <v>174000</v>
+      </c>
+      <c r="R27" s="31">
+        <v>153000</v>
+      </c>
+      <c r="S27" s="32">
+        <v>45500</v>
+      </c>
+      <c r="T27" s="29">
+        <v>130</v>
+      </c>
+      <c r="U27" s="29">
+        <v>490</v>
+      </c>
+      <c r="V27" s="29">
+        <v>365</v>
+      </c>
+      <c r="W27" s="29"/>
+    </row>
+    <row r="28" spans="1:23">
+      <c r="A28" s="7">
+        <v>26</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="29">
+        <v>1350</v>
+      </c>
+      <c r="D28" s="33">
+        <v>1285</v>
+      </c>
+      <c r="E28" s="29">
+        <v>1300</v>
+      </c>
+      <c r="H28" s="35">
+        <v>10000</v>
+      </c>
+      <c r="M28" s="29"/>
+      <c r="N28" s="30">
+        <v>242000</v>
+      </c>
+      <c r="O28" s="31">
+        <v>253000</v>
+      </c>
+      <c r="P28" s="32">
+        <v>174000</v>
+      </c>
+      <c r="Q28" s="32">
+        <v>182000</v>
+      </c>
+      <c r="R28" s="31">
+        <v>160000</v>
+      </c>
+      <c r="S28" s="32">
+        <v>47500</v>
+      </c>
+      <c r="T28" s="29">
+        <v>135</v>
+      </c>
+      <c r="U28" s="29">
+        <v>510</v>
+      </c>
+      <c r="V28" s="29">
+        <v>380</v>
+      </c>
+      <c r="W28" s="29"/>
+    </row>
+    <row r="29" spans="1:23">
+      <c r="A29" s="7">
+        <v>27</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="29">
+        <v>1400</v>
+      </c>
+      <c r="D29" s="33">
+        <v>1335</v>
+      </c>
+      <c r="E29" s="29">
+        <v>1350</v>
+      </c>
+      <c r="H29" s="35">
+        <v>10400</v>
+      </c>
+      <c r="M29" s="29"/>
+      <c r="N29" s="30">
+        <v>253000</v>
+      </c>
+      <c r="O29" s="31">
+        <v>264000</v>
+      </c>
+      <c r="P29" s="32">
+        <v>182000</v>
+      </c>
+      <c r="Q29" s="32">
+        <v>190000</v>
+      </c>
+      <c r="R29" s="31">
+        <v>167000</v>
+      </c>
+      <c r="S29" s="32">
+        <v>49500</v>
+      </c>
+      <c r="T29" s="29">
+        <v>140</v>
+      </c>
+      <c r="U29" s="29">
+        <v>530</v>
+      </c>
+      <c r="V29" s="29">
+        <v>395</v>
+      </c>
+      <c r="W29" s="29"/>
+    </row>
+    <row r="30" spans="1:23">
+      <c r="A30" s="7">
+        <v>28</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="29">
+        <v>1450</v>
+      </c>
+      <c r="D30" s="33">
+        <v>1385</v>
+      </c>
+      <c r="E30" s="29">
+        <v>1400</v>
+      </c>
+      <c r="H30" s="35">
+        <v>10800</v>
+      </c>
+      <c r="M30" s="29"/>
+      <c r="N30" s="30">
+        <v>264000</v>
+      </c>
+      <c r="O30" s="31">
+        <v>275000</v>
+      </c>
+      <c r="P30" s="32">
+        <v>190000</v>
+      </c>
+      <c r="Q30" s="32">
+        <v>198000</v>
+      </c>
+      <c r="R30" s="31">
+        <v>174000</v>
+      </c>
+      <c r="S30" s="32">
+        <v>51500</v>
+      </c>
+      <c r="T30" s="29">
+        <v>145</v>
+      </c>
+      <c r="U30" s="29">
+        <v>550</v>
+      </c>
+      <c r="V30" s="29">
+        <v>410</v>
+      </c>
+      <c r="W30" s="29"/>
+    </row>
+    <row r="31" spans="1:23">
+      <c r="A31" s="7">
+        <v>29</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="29">
+        <v>1500</v>
+      </c>
+      <c r="D31" s="33">
+        <v>1435</v>
+      </c>
+      <c r="E31" s="29">
+        <v>1450</v>
+      </c>
+      <c r="H31" s="35">
+        <v>11200</v>
+      </c>
+      <c r="M31" s="29"/>
+      <c r="N31" s="30">
+        <v>275000</v>
+      </c>
+      <c r="O31" s="31">
+        <v>286000</v>
+      </c>
+      <c r="P31" s="32">
+        <v>198000</v>
+      </c>
+      <c r="Q31" s="32">
+        <v>206000</v>
+      </c>
+      <c r="R31" s="31">
+        <v>181000</v>
+      </c>
+      <c r="S31" s="32">
+        <v>53500</v>
+      </c>
+      <c r="T31" s="29">
+        <v>150</v>
+      </c>
+      <c r="U31" s="29">
+        <v>570</v>
+      </c>
+      <c r="V31" s="29">
+        <v>425</v>
+      </c>
+      <c r="W31" s="29"/>
+    </row>
+    <row r="32" spans="1:23">
+      <c r="A32" s="7">
+        <v>30</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="29">
+        <v>1530</v>
+      </c>
+      <c r="D32" s="29">
+        <v>1485</v>
+      </c>
+      <c r="E32" s="29">
+        <v>1500</v>
+      </c>
+      <c r="H32" s="35">
+        <v>11600</v>
+      </c>
+      <c r="M32" s="29"/>
+      <c r="N32" s="30">
+        <v>286000</v>
+      </c>
+      <c r="O32" s="31">
+        <v>297000</v>
+      </c>
+      <c r="P32" s="32">
+        <v>206000</v>
+      </c>
+      <c r="Q32" s="32">
+        <v>214000</v>
+      </c>
+      <c r="R32" s="31">
+        <v>188000</v>
+      </c>
+      <c r="S32" s="32">
+        <v>55500</v>
+      </c>
+      <c r="T32" s="29">
+        <v>155</v>
+      </c>
+      <c r="U32" s="29">
+        <v>590</v>
+      </c>
+      <c r="V32" s="29">
+        <v>440</v>
+      </c>
+      <c r="W32" s="29"/>
+    </row>
+    <row r="33" spans="8:21">
+      <c r="H33" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="N33" s="28"/>
+      <c r="O33" s="28"/>
+      <c r="P33" s="28"/>
+      <c r="Q33" s="28"/>
+      <c r="R33" s="28"/>
+      <c r="U33" s="23" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/돌발 노출 조건 정리.xlsx
+++ b/돌발 노출 조건 정리.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\투캉 공유 폴더\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kodol\Desktop\투캉 공용 폴더\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED4607D-7C7C-4817-AD55-FF740A428166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B8A38E-8F5C-43A2-910D-0F9683D0B6A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44130" yWindow="2475" windowWidth="23070" windowHeight="15480" activeTab="1" xr2:uid="{03183270-ED35-4CBA-B934-C51A3B93B442}"/>
+    <workbookView xWindow="-21570" yWindow="3270" windowWidth="21570" windowHeight="15480" activeTab="1" xr2:uid="{03183270-ED35-4CBA-B934-C51A3B93B442}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="테스트" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="132">
   <si>
     <r>
       <t>도철</t>
@@ -791,6 +792,70 @@
   </si>
   <si>
     <t>8000[206스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>17000[227스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>240[246스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>23[246스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>50[246스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>20[246스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>300[246스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>고대1 (5)[246스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>고대1 (14)[246스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>250[254스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000[259스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>11000[259스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>14000[259스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>8000[282스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>11000[285스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>70[288스테]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4000[291스테]</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -991,7 +1056,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1077,19 +1142,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1100,6 +1156,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3312,7 +3371,7 @@
     <col min="10" max="10" width="16.875" style="8" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14" style="8" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.875" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.875" style="8" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.25" style="8" bestFit="1" customWidth="1"/>
     <col min="15" max="19" width="14.375" style="8" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="11.75" style="8" bestFit="1" customWidth="1"/>
@@ -3476,52 +3535,52 @@
       <c r="C3" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="33">
+      <c r="D3" s="1">
         <v>35</v>
       </c>
-      <c r="E3" s="29">
+      <c r="E3" s="8">
         <v>50</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="F3" s="31" t="s">
         <v>101</v>
       </c>
       <c r="G3" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="H3" s="35">
+      <c r="H3" s="32">
         <v>200</v>
       </c>
-      <c r="I3" s="29">
+      <c r="I3" s="8">
         <v>1</v>
       </c>
-      <c r="J3" s="29">
+      <c r="J3" s="8">
         <v>1000</v>
       </c>
-      <c r="K3" s="29">
+      <c r="K3" s="8">
         <v>1</v>
       </c>
-      <c r="L3" s="29">
+      <c r="L3" s="8">
         <v>1000</v>
       </c>
-      <c r="M3" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="N3" s="36" t="s">
+      <c r="M3" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="N3" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="O3" s="31">
-        <v>4000</v>
-      </c>
-      <c r="P3" s="34" t="s">
+      <c r="O3" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="P3" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="Q3" s="34" t="s">
+      <c r="Q3" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="R3" s="31">
-        <v>300</v>
-      </c>
-      <c r="S3" s="32">
+      <c r="R3" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="S3" s="30">
         <v>200</v>
       </c>
       <c r="T3" s="16" t="s">
@@ -3533,7 +3592,7 @@
       <c r="V3" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="W3" s="33" t="s">
+      <c r="W3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -3547,52 +3606,52 @@
       <c r="C4" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="1">
         <v>85</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="8">
         <v>100</v>
       </c>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="31" t="s">
         <v>111</v>
       </c>
       <c r="G4" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="H4" s="35">
+      <c r="H4" s="32">
         <v>400</v>
       </c>
-      <c r="I4" s="29">
+      <c r="I4" s="8">
         <v>100</v>
       </c>
-      <c r="J4" s="29">
+      <c r="J4" s="8">
         <v>2000</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="8">
         <v>100</v>
       </c>
-      <c r="L4" s="29">
+      <c r="L4" s="8">
         <v>2000</v>
       </c>
-      <c r="M4" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="N4" s="36" t="s">
+      <c r="M4" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="N4" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="O4" s="31">
+      <c r="O4" s="29">
         <v>7000</v>
       </c>
-      <c r="P4" s="34" t="s">
+      <c r="P4" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="Q4" s="34" t="s">
+      <c r="Q4" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="R4" s="31">
+      <c r="R4" s="29">
         <v>2000</v>
       </c>
-      <c r="S4" s="32">
+      <c r="S4" s="30">
         <v>1000</v>
       </c>
       <c r="T4" s="16" t="s">
@@ -3601,10 +3660,10 @@
       <c r="U4" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="V4" s="29">
-        <v>20</v>
-      </c>
-      <c r="W4" s="33" t="s">
+      <c r="V4" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="W4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3618,64 +3677,64 @@
       <c r="C5" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="1">
         <v>135</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="8">
         <v>150</v>
       </c>
-      <c r="F5" s="32">
+      <c r="F5" s="30">
         <v>4000</v>
       </c>
       <c r="G5" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="H5" s="35">
+      <c r="H5" s="32">
         <v>800</v>
       </c>
-      <c r="I5" s="29">
+      <c r="I5" s="8">
         <v>200</v>
       </c>
-      <c r="J5" s="29">
+      <c r="J5" s="8">
         <v>3000</v>
       </c>
-      <c r="K5" s="29">
+      <c r="K5" s="8">
         <v>200</v>
       </c>
-      <c r="L5" s="29">
+      <c r="L5" s="8">
         <v>3000</v>
       </c>
-      <c r="M5" s="29" t="s">
+      <c r="M5" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="N5" s="36" t="s">
+      <c r="N5" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="O5" s="31">
+      <c r="O5" s="29">
         <v>12000</v>
       </c>
-      <c r="P5" s="32">
-        <v>5000</v>
-      </c>
-      <c r="Q5" s="34" t="s">
+      <c r="P5" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q5" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="R5" s="31">
+      <c r="R5" s="29">
         <v>4000</v>
       </c>
-      <c r="S5" s="32">
+      <c r="S5" s="30">
         <v>2000</v>
       </c>
       <c r="T5" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="U5" s="29">
-        <v>50</v>
-      </c>
-      <c r="V5" s="29">
+      <c r="U5" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="V5" s="8">
         <v>35</v>
       </c>
-      <c r="W5" s="33" t="s">
+      <c r="W5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -3686,67 +3745,67 @@
       <c r="B6" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="29">
-        <v>250</v>
-      </c>
-      <c r="D6" s="33">
+      <c r="C6" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" s="1">
         <v>185</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="8">
         <v>200</v>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="30">
         <v>8000</v>
       </c>
       <c r="G6" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="H6" s="35">
+      <c r="H6" s="32">
         <v>1200</v>
       </c>
-      <c r="I6" s="29">
+      <c r="I6" s="8">
         <v>300</v>
       </c>
-      <c r="J6" s="29">
+      <c r="J6" s="8">
         <v>4000</v>
       </c>
-      <c r="K6" s="29">
+      <c r="K6" s="8">
         <v>300</v>
       </c>
-      <c r="L6" s="29">
+      <c r="L6" s="8">
         <v>4000</v>
       </c>
-      <c r="M6" s="29" t="s">
+      <c r="M6" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="N6" s="36" t="s">
+      <c r="N6" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="O6" s="31">
+      <c r="O6" s="29">
         <v>17000</v>
       </c>
-      <c r="P6" s="32">
-        <v>8000</v>
-      </c>
-      <c r="Q6" s="32">
-        <v>11000</v>
-      </c>
-      <c r="R6" s="31">
+      <c r="P6" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q6" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="R6" s="29">
         <v>6000</v>
       </c>
-      <c r="S6" s="32">
+      <c r="S6" s="30">
         <v>3500</v>
       </c>
-      <c r="T6" s="29">
-        <v>23</v>
-      </c>
-      <c r="U6" s="29">
-        <v>70</v>
-      </c>
-      <c r="V6" s="29">
+      <c r="T6" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="U6" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="V6" s="8">
         <v>50</v>
       </c>
-      <c r="W6" s="33" t="s">
+      <c r="W6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3754,70 +3813,70 @@
       <c r="A7" s="7">
         <v>5</v>
       </c>
-      <c r="B7" s="29">
-        <v>240</v>
-      </c>
-      <c r="C7" s="29">
+      <c r="B7" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="8">
         <v>300</v>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="1">
         <v>235</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="8">
         <v>250</v>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="30">
         <v>12000</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="G7" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="35">
+      <c r="H7" s="32">
         <v>1600</v>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="8">
         <v>400</v>
       </c>
       <c r="J7" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="K7" s="29">
+      <c r="K7" s="8">
         <v>400</v>
       </c>
       <c r="L7" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="M7" s="29" t="s">
+      <c r="M7" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="N7" s="30">
-        <v>17000</v>
-      </c>
-      <c r="O7" s="31">
+      <c r="N7" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="O7" s="29">
         <v>22000</v>
       </c>
-      <c r="P7" s="32">
-        <v>11000</v>
-      </c>
-      <c r="Q7" s="32">
-        <v>14000</v>
-      </c>
-      <c r="R7" s="31">
+      <c r="P7" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q7" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="R7" s="29">
         <v>13000</v>
       </c>
-      <c r="S7" s="32">
+      <c r="S7" s="30">
         <v>5500</v>
       </c>
-      <c r="T7" s="29">
+      <c r="T7" s="8">
         <v>29</v>
       </c>
-      <c r="U7" s="29">
+      <c r="U7" s="8">
         <v>90</v>
       </c>
-      <c r="V7" s="29">
+      <c r="V7" s="8">
         <v>65</v>
       </c>
-      <c r="W7" s="33" t="s">
+      <c r="W7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3825,66 +3884,66 @@
       <c r="A8" s="7">
         <v>6</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="8">
         <v>315</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="8">
         <v>350</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="1">
         <v>285</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="8">
         <v>300</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="30">
         <v>16000</v>
       </c>
-      <c r="G8" s="29" t="s">
+      <c r="G8" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="35">
+      <c r="H8" s="32">
         <v>2000</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8" s="8">
         <v>500</v>
       </c>
       <c r="J8"/>
-      <c r="K8" s="29">
+      <c r="K8" s="8">
         <v>500</v>
       </c>
       <c r="L8"/>
-      <c r="M8" s="29" t="s">
+      <c r="M8" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="N8" s="30">
+      <c r="N8" s="9">
         <v>22000</v>
       </c>
-      <c r="O8" s="31">
+      <c r="O8" s="29">
         <v>33000</v>
       </c>
-      <c r="P8" s="32">
+      <c r="P8" s="30">
         <v>14000</v>
       </c>
-      <c r="Q8" s="32">
+      <c r="Q8" s="30">
         <v>22000</v>
       </c>
-      <c r="R8" s="31">
+      <c r="R8" s="29">
         <v>20000</v>
       </c>
-      <c r="S8" s="32">
+      <c r="S8" s="30">
         <v>7500</v>
       </c>
-      <c r="T8" s="29">
+      <c r="T8" s="8">
         <v>35</v>
       </c>
-      <c r="U8" s="29">
+      <c r="U8" s="8">
         <v>110</v>
       </c>
-      <c r="V8" s="29">
+      <c r="V8" s="8">
         <v>80</v>
       </c>
-      <c r="W8" s="33" t="s">
+      <c r="W8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3892,66 +3951,66 @@
       <c r="A9" s="7">
         <v>7</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="8">
         <v>375</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="8">
         <v>400</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="1">
         <v>335</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="8">
         <v>350</v>
       </c>
       <c r="F9" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="29" t="s">
+      <c r="G9" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="35">
+      <c r="H9" s="32">
         <v>2400</v>
       </c>
-      <c r="I9" s="29">
+      <c r="I9" s="8">
         <v>600</v>
       </c>
       <c r="J9"/>
-      <c r="K9" s="29">
+      <c r="K9" s="8">
         <v>600</v>
       </c>
       <c r="L9"/>
-      <c r="M9" s="29" t="s">
+      <c r="M9" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="N9" s="30">
+      <c r="N9" s="9">
         <v>33000</v>
       </c>
-      <c r="O9" s="31">
+      <c r="O9" s="29">
         <v>44000</v>
       </c>
-      <c r="P9" s="32">
+      <c r="P9" s="30">
         <v>22000</v>
       </c>
-      <c r="Q9" s="32">
+      <c r="Q9" s="30">
         <v>30000</v>
       </c>
-      <c r="R9" s="31">
+      <c r="R9" s="29">
         <v>27000</v>
       </c>
-      <c r="S9" s="32">
+      <c r="S9" s="30">
         <v>9500</v>
       </c>
-      <c r="T9" s="29">
+      <c r="T9" s="8">
         <v>40</v>
       </c>
-      <c r="U9" s="29">
+      <c r="U9" s="8">
         <v>130</v>
       </c>
-      <c r="V9" s="29">
+      <c r="V9" s="8">
         <v>95</v>
       </c>
-      <c r="W9" s="33" t="s">
+      <c r="W9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3959,66 +4018,66 @@
       <c r="A10" s="7">
         <v>8</v>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="8">
         <v>435</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="8">
         <v>450</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="1">
         <v>385</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="8">
         <v>400</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="9">
         <v>300</v>
       </c>
-      <c r="G10" s="29" t="s">
+      <c r="G10" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="35">
+      <c r="H10" s="32">
         <v>2800</v>
       </c>
-      <c r="I10" s="29">
+      <c r="I10" s="8">
         <v>700</v>
       </c>
       <c r="J10"/>
-      <c r="K10" s="29">
+      <c r="K10" s="8">
         <v>700</v>
       </c>
       <c r="L10"/>
-      <c r="M10" s="29" t="s">
+      <c r="M10" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="N10" s="30">
+      <c r="N10" s="9">
         <v>44000</v>
       </c>
-      <c r="O10" s="31">
+      <c r="O10" s="29">
         <v>55000</v>
       </c>
-      <c r="P10" s="32">
+      <c r="P10" s="30">
         <v>30000</v>
       </c>
-      <c r="Q10" s="32">
+      <c r="Q10" s="30">
         <v>38000</v>
       </c>
-      <c r="R10" s="31">
+      <c r="R10" s="29">
         <v>34000</v>
       </c>
-      <c r="S10" s="32">
+      <c r="S10" s="30">
         <v>11500</v>
       </c>
-      <c r="T10" s="29">
+      <c r="T10" s="8">
         <v>45</v>
       </c>
-      <c r="U10" s="29">
+      <c r="U10" s="8">
         <v>150</v>
       </c>
-      <c r="V10" s="29">
+      <c r="V10" s="8">
         <v>110</v>
       </c>
-      <c r="W10" s="33" t="s">
+      <c r="W10" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4026,66 +4085,66 @@
       <c r="A11" s="7">
         <v>9</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="8">
         <v>495</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="8">
         <v>500</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="1">
         <v>435</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="8">
         <v>450</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="9">
         <v>1000</v>
       </c>
-      <c r="G11" s="29" t="s">
+      <c r="G11" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="35">
+      <c r="H11" s="32">
         <v>3200</v>
       </c>
-      <c r="I11" s="29">
+      <c r="I11" s="8">
         <v>800</v>
       </c>
       <c r="J11"/>
-      <c r="K11" s="29">
+      <c r="K11" s="8">
         <v>800</v>
       </c>
       <c r="L11"/>
-      <c r="M11" s="29" t="s">
+      <c r="M11" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="N11" s="30">
+      <c r="N11" s="9">
         <v>55000</v>
       </c>
-      <c r="O11" s="31">
+      <c r="O11" s="29">
         <v>66000</v>
       </c>
-      <c r="P11" s="32">
+      <c r="P11" s="30">
         <v>38000</v>
       </c>
-      <c r="Q11" s="32">
+      <c r="Q11" s="30">
         <v>46000</v>
       </c>
-      <c r="R11" s="31">
+      <c r="R11" s="29">
         <v>41000</v>
       </c>
-      <c r="S11" s="32">
+      <c r="S11" s="30">
         <v>13500</v>
       </c>
-      <c r="T11" s="29">
+      <c r="T11" s="8">
         <v>50</v>
       </c>
-      <c r="U11" s="29">
+      <c r="U11" s="8">
         <v>170</v>
       </c>
-      <c r="V11" s="29">
+      <c r="V11" s="8">
         <v>125</v>
       </c>
-      <c r="W11" s="33" t="s">
+      <c r="W11" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4093,66 +4152,66 @@
       <c r="A12" s="7">
         <v>10</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="8">
         <v>575</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="8">
         <v>550</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="1">
         <v>485</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="8">
         <v>500</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="9">
         <v>4000</v>
       </c>
-      <c r="G12" s="29" t="s">
+      <c r="G12" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="H12" s="35">
+      <c r="H12" s="32">
         <v>3600</v>
       </c>
-      <c r="I12" s="29">
+      <c r="I12" s="8">
         <v>900</v>
       </c>
       <c r="J12"/>
-      <c r="K12" s="29">
+      <c r="K12" s="8">
         <v>900</v>
       </c>
       <c r="L12"/>
-      <c r="M12" s="29" t="s">
+      <c r="M12" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="N12" s="30">
+      <c r="N12" s="9">
         <v>66000</v>
       </c>
-      <c r="O12" s="31">
+      <c r="O12" s="29">
         <v>77000</v>
       </c>
-      <c r="P12" s="32">
+      <c r="P12" s="30">
         <v>46000</v>
       </c>
-      <c r="Q12" s="32">
+      <c r="Q12" s="30">
         <v>54000</v>
       </c>
-      <c r="R12" s="31">
+      <c r="R12" s="29">
         <v>48000</v>
       </c>
-      <c r="S12" s="32">
+      <c r="S12" s="30">
         <v>15500</v>
       </c>
-      <c r="T12" s="29">
+      <c r="T12" s="8">
         <v>55</v>
       </c>
-      <c r="U12" s="29">
+      <c r="U12" s="8">
         <v>190</v>
       </c>
-      <c r="V12" s="29">
+      <c r="V12" s="8">
         <v>140</v>
       </c>
-      <c r="W12" s="33" t="s">
+      <c r="W12" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4163,22 +4222,22 @@
       <c r="B13" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="8">
         <v>600</v>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="1">
         <v>535</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="8">
         <v>550</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="9">
         <v>6000</v>
       </c>
-      <c r="G13" s="29" t="s">
+      <c r="G13" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="H13" s="35">
+      <c r="H13" s="32">
         <v>4000</v>
       </c>
       <c r="I13" s="24" t="s">
@@ -4189,37 +4248,37 @@
         <v>86</v>
       </c>
       <c r="L13"/>
-      <c r="M13" s="29" t="s">
+      <c r="M13" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="N13" s="30">
+      <c r="N13" s="9">
         <v>77000</v>
       </c>
-      <c r="O13" s="31">
+      <c r="O13" s="29">
         <v>88000</v>
       </c>
-      <c r="P13" s="32">
+      <c r="P13" s="30">
         <v>54000</v>
       </c>
-      <c r="Q13" s="32">
+      <c r="Q13" s="30">
         <v>62000</v>
       </c>
-      <c r="R13" s="31">
+      <c r="R13" s="29">
         <v>55000</v>
       </c>
-      <c r="S13" s="32">
+      <c r="S13" s="30">
         <v>17500</v>
       </c>
-      <c r="T13" s="29">
+      <c r="T13" s="8">
         <v>60</v>
       </c>
-      <c r="U13" s="29">
+      <c r="U13" s="8">
         <v>210</v>
       </c>
-      <c r="V13" s="29">
+      <c r="V13" s="8">
         <v>155</v>
       </c>
-      <c r="W13" s="33" t="s">
+      <c r="W13" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4227,54 +4286,54 @@
       <c r="A14" s="7">
         <v>12</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="8">
         <v>650</v>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="1">
         <v>585</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="8">
         <v>600</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="9">
         <v>8000</v>
       </c>
-      <c r="H14" s="35">
+      <c r="H14" s="32">
         <v>4400</v>
       </c>
       <c r="J14"/>
       <c r="L14"/>
-      <c r="M14" s="29" t="s">
+      <c r="M14" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="N14" s="30">
+      <c r="N14" s="9">
         <v>88000</v>
       </c>
-      <c r="O14" s="31">
+      <c r="O14" s="29">
         <v>99000</v>
       </c>
-      <c r="P14" s="32">
+      <c r="P14" s="30">
         <v>62000</v>
       </c>
-      <c r="Q14" s="32">
+      <c r="Q14" s="30">
         <v>70000</v>
       </c>
-      <c r="R14" s="31">
+      <c r="R14" s="29">
         <v>62000</v>
       </c>
-      <c r="S14" s="32">
+      <c r="S14" s="30">
         <v>19500</v>
       </c>
-      <c r="T14" s="29">
+      <c r="T14" s="8">
         <v>65</v>
       </c>
-      <c r="U14" s="29">
+      <c r="U14" s="8">
         <v>230</v>
       </c>
-      <c r="V14" s="29">
+      <c r="V14" s="8">
         <v>170</v>
       </c>
-      <c r="W14" s="33" t="s">
+      <c r="W14" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -4282,54 +4341,54 @@
       <c r="A15" s="7">
         <v>13</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="8">
         <v>700</v>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="1">
         <v>635</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="8">
         <v>650</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="9">
         <v>10000</v>
       </c>
-      <c r="H15" s="35">
+      <c r="H15" s="32">
         <v>4800</v>
       </c>
       <c r="J15"/>
       <c r="L15"/>
-      <c r="M15" s="29" t="s">
+      <c r="M15" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="N15" s="30">
+      <c r="N15" s="9">
         <v>99000</v>
       </c>
-      <c r="O15" s="31">
+      <c r="O15" s="29">
         <v>110000</v>
       </c>
-      <c r="P15" s="32">
+      <c r="P15" s="30">
         <v>70000</v>
       </c>
-      <c r="Q15" s="32">
+      <c r="Q15" s="30">
         <v>78000</v>
       </c>
-      <c r="R15" s="31">
+      <c r="R15" s="29">
         <v>69000</v>
       </c>
-      <c r="S15" s="32">
+      <c r="S15" s="30">
         <v>21500</v>
       </c>
-      <c r="T15" s="29">
+      <c r="T15" s="8">
         <v>70</v>
       </c>
-      <c r="U15" s="29">
+      <c r="U15" s="8">
         <v>250</v>
       </c>
-      <c r="V15" s="29">
+      <c r="V15" s="8">
         <v>185</v>
       </c>
-      <c r="W15" s="33" t="s">
+      <c r="W15" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -4337,54 +4396,54 @@
       <c r="A16" s="7">
         <v>14</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="8">
         <v>750</v>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="1">
         <v>685</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="8">
         <v>700</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="9">
         <v>12000</v>
       </c>
-      <c r="H16" s="35">
+      <c r="H16" s="32">
         <v>5200</v>
       </c>
       <c r="J16"/>
       <c r="L16"/>
-      <c r="M16" s="29" t="s">
+      <c r="M16" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="N16" s="30">
+      <c r="N16" s="9">
         <v>110000</v>
       </c>
-      <c r="O16" s="31">
+      <c r="O16" s="29">
         <v>121000</v>
       </c>
-      <c r="P16" s="32">
+      <c r="P16" s="30">
         <v>78000</v>
       </c>
-      <c r="Q16" s="32">
+      <c r="Q16" s="30">
         <v>86000</v>
       </c>
-      <c r="R16" s="31">
+      <c r="R16" s="29">
         <v>76000</v>
       </c>
-      <c r="S16" s="32">
+      <c r="S16" s="30">
         <v>23500</v>
       </c>
-      <c r="T16" s="29">
+      <c r="T16" s="8">
         <v>75</v>
       </c>
-      <c r="U16" s="29">
+      <c r="U16" s="8">
         <v>270</v>
       </c>
-      <c r="V16" s="29">
+      <c r="V16" s="8">
         <v>200</v>
       </c>
-      <c r="W16" s="33" t="s">
+      <c r="W16" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4392,54 +4451,54 @@
       <c r="A17" s="7">
         <v>15</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="8">
         <v>800</v>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="1">
         <v>735</v>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="8">
         <v>750</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="9">
         <v>14000</v>
       </c>
-      <c r="H17" s="35">
+      <c r="H17" s="32">
         <v>5600</v>
       </c>
       <c r="J17"/>
       <c r="L17"/>
-      <c r="M17" s="29" t="s">
+      <c r="M17" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="N17" s="30">
+      <c r="N17" s="9">
         <v>121000</v>
       </c>
-      <c r="O17" s="31">
+      <c r="O17" s="29">
         <v>132000</v>
       </c>
-      <c r="P17" s="32">
+      <c r="P17" s="30">
         <v>86000</v>
       </c>
-      <c r="Q17" s="32">
+      <c r="Q17" s="30">
         <v>94000</v>
       </c>
-      <c r="R17" s="31">
+      <c r="R17" s="29">
         <v>83000</v>
       </c>
-      <c r="S17" s="32">
+      <c r="S17" s="30">
         <v>25500</v>
       </c>
-      <c r="T17" s="29">
+      <c r="T17" s="8">
         <v>80</v>
       </c>
-      <c r="U17" s="29">
+      <c r="U17" s="8">
         <v>290</v>
       </c>
-      <c r="V17" s="29">
+      <c r="V17" s="8">
         <v>215</v>
       </c>
-      <c r="W17" s="33" t="s">
+      <c r="W17" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -4447,54 +4506,54 @@
       <c r="A18" s="7">
         <v>16</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="8">
         <v>850</v>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="1">
         <v>785</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="8">
         <v>800</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="9">
         <v>16000</v>
       </c>
-      <c r="H18" s="35">
+      <c r="H18" s="32">
         <v>6000</v>
       </c>
       <c r="J18"/>
       <c r="L18"/>
-      <c r="M18" s="29" t="s">
+      <c r="M18" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="N18" s="30">
+      <c r="N18" s="9">
         <v>132000</v>
       </c>
-      <c r="O18" s="31">
+      <c r="O18" s="29">
         <v>143000</v>
       </c>
-      <c r="P18" s="32">
+      <c r="P18" s="30">
         <v>94000</v>
       </c>
-      <c r="Q18" s="32">
+      <c r="Q18" s="30">
         <v>102000</v>
       </c>
-      <c r="R18" s="31">
+      <c r="R18" s="29">
         <v>90000</v>
       </c>
-      <c r="S18" s="32">
+      <c r="S18" s="30">
         <v>27500</v>
       </c>
-      <c r="T18" s="29">
+      <c r="T18" s="8">
         <v>85</v>
       </c>
-      <c r="U18" s="29">
+      <c r="U18" s="8">
         <v>310</v>
       </c>
-      <c r="V18" s="29">
+      <c r="V18" s="8">
         <v>230</v>
       </c>
-      <c r="W18" s="33" t="s">
+      <c r="W18" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4503,684 +4562,659 @@
         <v>17</v>
       </c>
       <c r="B19" s="1"/>
-      <c r="C19" s="29">
+      <c r="C19" s="8">
         <v>900</v>
       </c>
-      <c r="D19" s="33">
+      <c r="D19" s="1">
         <v>835</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="8">
         <v>850</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="9">
         <v>18000</v>
       </c>
-      <c r="H19" s="35">
+      <c r="H19" s="32">
         <v>6400</v>
       </c>
       <c r="J19"/>
       <c r="L19"/>
-      <c r="M19" s="29" t="s">
+      <c r="M19" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="N19" s="30">
+      <c r="N19" s="9">
         <v>143000</v>
       </c>
-      <c r="O19" s="31">
+      <c r="O19" s="29">
         <v>154000</v>
       </c>
-      <c r="P19" s="32">
+      <c r="P19" s="30">
         <v>102000</v>
       </c>
-      <c r="Q19" s="32">
+      <c r="Q19" s="30">
         <v>110000</v>
       </c>
-      <c r="R19" s="31">
+      <c r="R19" s="29">
         <v>97000</v>
       </c>
-      <c r="S19" s="32">
+      <c r="S19" s="30">
         <v>29500</v>
       </c>
-      <c r="T19" s="29">
+      <c r="T19" s="8">
         <v>90</v>
       </c>
-      <c r="U19" s="29">
+      <c r="U19" s="8">
         <v>330</v>
       </c>
-      <c r="V19" s="29">
+      <c r="V19" s="8">
         <v>245</v>
       </c>
-      <c r="W19" s="29"/>
     </row>
     <row r="20" spans="1:23">
       <c r="A20" s="7">
         <v>18</v>
       </c>
       <c r="B20" s="1"/>
-      <c r="C20" s="29">
+      <c r="C20" s="8">
         <v>950</v>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="1">
         <v>885</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="8">
         <v>900</v>
       </c>
       <c r="F20" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="H20" s="35">
+      <c r="H20" s="32">
         <v>6800</v>
       </c>
       <c r="J20"/>
       <c r="K20"/>
       <c r="L20"/>
-      <c r="M20" s="29" t="s">
+      <c r="M20" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="N20" s="30">
+      <c r="N20" s="9">
         <v>154000</v>
       </c>
-      <c r="O20" s="31">
+      <c r="O20" s="29">
         <v>165000</v>
       </c>
-      <c r="P20" s="32">
+      <c r="P20" s="30">
         <v>110000</v>
       </c>
-      <c r="Q20" s="32">
+      <c r="Q20" s="30">
         <v>118000</v>
       </c>
-      <c r="R20" s="31">
+      <c r="R20" s="29">
         <v>104000</v>
       </c>
-      <c r="S20" s="32">
+      <c r="S20" s="30">
         <v>31500</v>
       </c>
-      <c r="T20" s="29">
+      <c r="T20" s="8">
         <v>95</v>
       </c>
-      <c r="U20" s="29">
+      <c r="U20" s="8">
         <v>350</v>
       </c>
-      <c r="V20" s="29">
+      <c r="V20" s="8">
         <v>260</v>
       </c>
-      <c r="W20" s="29"/>
     </row>
     <row r="21" spans="1:23">
       <c r="A21" s="7">
         <v>19</v>
       </c>
       <c r="B21" s="1"/>
-      <c r="C21" s="29">
+      <c r="C21" s="8">
         <v>1000</v>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="1">
         <v>935</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="8">
         <v>950</v>
       </c>
       <c r="F21"/>
-      <c r="H21" s="35">
+      <c r="H21" s="32">
         <v>7200</v>
       </c>
       <c r="J21"/>
       <c r="K21"/>
       <c r="L21"/>
-      <c r="M21" s="29"/>
-      <c r="N21" s="30">
+      <c r="N21" s="9">
         <v>165000</v>
       </c>
-      <c r="O21" s="31">
+      <c r="O21" s="29">
         <v>176000</v>
       </c>
-      <c r="P21" s="32">
+      <c r="P21" s="30">
         <v>118000</v>
       </c>
-      <c r="Q21" s="32">
+      <c r="Q21" s="30">
         <v>126000</v>
       </c>
-      <c r="R21" s="31">
+      <c r="R21" s="29">
         <v>111000</v>
       </c>
-      <c r="S21" s="32">
+      <c r="S21" s="30">
         <v>33500</v>
       </c>
-      <c r="T21" s="29">
+      <c r="T21" s="8">
         <v>100</v>
       </c>
-      <c r="U21" s="29">
+      <c r="U21" s="8">
         <v>370</v>
       </c>
-      <c r="V21" s="29">
+      <c r="V21" s="8">
         <v>275</v>
       </c>
-      <c r="W21" s="29"/>
     </row>
     <row r="22" spans="1:23">
       <c r="A22" s="7">
         <v>20</v>
       </c>
       <c r="B22" s="1"/>
-      <c r="C22" s="29">
+      <c r="C22" s="8">
         <v>1050</v>
       </c>
-      <c r="D22" s="33">
+      <c r="D22" s="1">
         <v>985</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="8">
         <v>1000</v>
       </c>
       <c r="F22"/>
-      <c r="H22" s="35">
+      <c r="H22" s="32">
         <v>7600</v>
       </c>
       <c r="J22"/>
       <c r="K22"/>
       <c r="L22"/>
-      <c r="M22" s="29"/>
-      <c r="N22" s="30">
+      <c r="N22" s="9">
         <v>176000</v>
       </c>
-      <c r="O22" s="31">
+      <c r="O22" s="29">
         <v>187000</v>
       </c>
-      <c r="P22" s="32">
+      <c r="P22" s="30">
         <v>126000</v>
       </c>
-      <c r="Q22" s="32">
+      <c r="Q22" s="30">
         <v>134000</v>
       </c>
-      <c r="R22" s="31">
+      <c r="R22" s="29">
         <v>118000</v>
       </c>
-      <c r="S22" s="32">
+      <c r="S22" s="30">
         <v>35500</v>
       </c>
-      <c r="T22" s="29">
+      <c r="T22" s="8">
         <v>105</v>
       </c>
-      <c r="U22" s="29">
+      <c r="U22" s="8">
         <v>390</v>
       </c>
-      <c r="V22" s="29">
+      <c r="V22" s="8">
         <v>290</v>
       </c>
-      <c r="W22" s="30"/>
+      <c r="W22" s="9"/>
     </row>
     <row r="23" spans="1:23">
       <c r="A23" s="7">
         <v>21</v>
       </c>
       <c r="B23" s="1"/>
-      <c r="C23" s="29">
+      <c r="C23" s="8">
         <v>1100</v>
       </c>
-      <c r="D23" s="33">
+      <c r="D23" s="1">
         <v>1035</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="8">
         <v>1050</v>
       </c>
       <c r="F23"/>
-      <c r="H23" s="35">
+      <c r="H23" s="32">
         <v>8000</v>
       </c>
-      <c r="M23" s="29"/>
-      <c r="N23" s="30">
+      <c r="N23" s="9">
         <v>187000</v>
       </c>
-      <c r="O23" s="31">
+      <c r="O23" s="29">
         <v>198000</v>
       </c>
-      <c r="P23" s="32">
+      <c r="P23" s="30">
         <v>134000</v>
       </c>
-      <c r="Q23" s="32">
+      <c r="Q23" s="30">
         <v>142000</v>
       </c>
-      <c r="R23" s="31">
+      <c r="R23" s="29">
         <v>125000</v>
       </c>
-      <c r="S23" s="32">
+      <c r="S23" s="30">
         <v>37500</v>
       </c>
-      <c r="T23" s="29">
+      <c r="T23" s="8">
         <v>110</v>
       </c>
-      <c r="U23" s="29">
+      <c r="U23" s="8">
         <v>410</v>
       </c>
-      <c r="V23" s="29">
+      <c r="V23" s="8">
         <v>305</v>
       </c>
-      <c r="W23" s="29"/>
     </row>
     <row r="24" spans="1:23">
       <c r="A24" s="7">
         <v>22</v>
       </c>
       <c r="B24" s="1"/>
-      <c r="C24" s="29">
+      <c r="C24" s="8">
         <v>1150</v>
       </c>
-      <c r="D24" s="33">
+      <c r="D24" s="1">
         <v>1085</v>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="8">
         <v>1100</v>
       </c>
-      <c r="H24" s="35">
+      <c r="H24" s="32">
         <v>8400</v>
       </c>
       <c r="J24" s="19"/>
-      <c r="M24" s="29"/>
-      <c r="N24" s="30">
+      <c r="N24" s="9">
         <v>198000</v>
       </c>
-      <c r="O24" s="31">
+      <c r="O24" s="29">
         <v>209000</v>
       </c>
-      <c r="P24" s="32">
+      <c r="P24" s="30">
         <v>142000</v>
       </c>
-      <c r="Q24" s="32">
+      <c r="Q24" s="30">
         <v>150000</v>
       </c>
-      <c r="R24" s="31">
+      <c r="R24" s="29">
         <v>132000</v>
       </c>
-      <c r="S24" s="32">
+      <c r="S24" s="30">
         <v>39500</v>
       </c>
-      <c r="T24" s="29">
+      <c r="T24" s="8">
         <v>115</v>
       </c>
-      <c r="U24" s="29">
+      <c r="U24" s="8">
         <v>430</v>
       </c>
-      <c r="V24" s="29">
+      <c r="V24" s="8">
         <v>320</v>
       </c>
-      <c r="W24" s="29"/>
     </row>
     <row r="25" spans="1:23">
       <c r="A25" s="7">
         <v>23</v>
       </c>
       <c r="B25" s="1"/>
-      <c r="C25" s="29">
+      <c r="C25" s="8">
         <v>1200</v>
       </c>
-      <c r="D25" s="33">
+      <c r="D25" s="1">
         <v>1135</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="8">
         <v>1150</v>
       </c>
-      <c r="H25" s="35">
+      <c r="H25" s="32">
         <v>8800</v>
       </c>
-      <c r="M25" s="29"/>
-      <c r="N25" s="30">
+      <c r="N25" s="9">
         <v>209000</v>
       </c>
-      <c r="O25" s="31">
+      <c r="O25" s="29">
         <v>220000</v>
       </c>
-      <c r="P25" s="32">
+      <c r="P25" s="30">
         <v>150000</v>
       </c>
-      <c r="Q25" s="32">
+      <c r="Q25" s="30">
         <v>158000</v>
       </c>
-      <c r="R25" s="31">
+      <c r="R25" s="29">
         <v>139000</v>
       </c>
-      <c r="S25" s="32">
+      <c r="S25" s="30">
         <v>41500</v>
       </c>
-      <c r="T25" s="29">
+      <c r="T25" s="8">
         <v>120</v>
       </c>
-      <c r="U25" s="29">
+      <c r="U25" s="8">
         <v>450</v>
       </c>
-      <c r="V25" s="29">
+      <c r="V25" s="8">
         <v>335</v>
       </c>
-      <c r="W25" s="29"/>
     </row>
     <row r="26" spans="1:23">
       <c r="A26" s="7">
         <v>24</v>
       </c>
       <c r="B26" s="1"/>
-      <c r="C26" s="29">
+      <c r="C26" s="8">
         <v>1250</v>
       </c>
-      <c r="D26" s="33">
+      <c r="D26" s="1">
         <v>1185</v>
       </c>
-      <c r="E26" s="29">
+      <c r="E26" s="8">
         <v>1200</v>
       </c>
-      <c r="H26" s="35">
+      <c r="H26" s="32">
         <v>9200</v>
       </c>
       <c r="J26" s="19"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="30">
+      <c r="N26" s="9">
         <v>220000</v>
       </c>
-      <c r="O26" s="31">
+      <c r="O26" s="29">
         <v>231000</v>
       </c>
-      <c r="P26" s="32">
+      <c r="P26" s="30">
         <v>158000</v>
       </c>
-      <c r="Q26" s="32">
+      <c r="Q26" s="30">
         <v>166000</v>
       </c>
-      <c r="R26" s="31">
+      <c r="R26" s="29">
         <v>146000</v>
       </c>
-      <c r="S26" s="32">
+      <c r="S26" s="30">
         <v>43500</v>
       </c>
-      <c r="T26" s="29">
+      <c r="T26" s="8">
         <v>125</v>
       </c>
-      <c r="U26" s="29">
+      <c r="U26" s="8">
         <v>470</v>
       </c>
-      <c r="V26" s="29">
+      <c r="V26" s="8">
         <v>350</v>
       </c>
-      <c r="W26" s="29"/>
     </row>
     <row r="27" spans="1:23">
       <c r="A27" s="7">
         <v>25</v>
       </c>
       <c r="B27" s="1"/>
-      <c r="C27" s="29">
+      <c r="C27" s="8">
         <v>1300</v>
       </c>
-      <c r="D27" s="33">
+      <c r="D27" s="1">
         <v>1235</v>
       </c>
-      <c r="E27" s="29">
+      <c r="E27" s="8">
         <v>1250</v>
       </c>
-      <c r="H27" s="35">
+      <c r="H27" s="32">
         <v>9600</v>
       </c>
-      <c r="M27" s="29"/>
-      <c r="N27" s="30">
+      <c r="N27" s="9">
         <v>231000</v>
       </c>
-      <c r="O27" s="31">
+      <c r="O27" s="29">
         <v>242000</v>
       </c>
-      <c r="P27" s="32">
+      <c r="P27" s="30">
         <v>166000</v>
       </c>
-      <c r="Q27" s="32">
+      <c r="Q27" s="30">
         <v>174000</v>
       </c>
-      <c r="R27" s="31">
+      <c r="R27" s="29">
         <v>153000</v>
       </c>
-      <c r="S27" s="32">
+      <c r="S27" s="30">
         <v>45500</v>
       </c>
-      <c r="T27" s="29">
+      <c r="T27" s="8">
         <v>130</v>
       </c>
-      <c r="U27" s="29">
+      <c r="U27" s="8">
         <v>490</v>
       </c>
-      <c r="V27" s="29">
+      <c r="V27" s="8">
         <v>365</v>
       </c>
-      <c r="W27" s="29"/>
     </row>
     <row r="28" spans="1:23">
       <c r="A28" s="7">
         <v>26</v>
       </c>
       <c r="B28" s="1"/>
-      <c r="C28" s="29">
+      <c r="C28" s="8">
         <v>1350</v>
       </c>
-      <c r="D28" s="33">
+      <c r="D28" s="1">
         <v>1285</v>
       </c>
-      <c r="E28" s="29">
+      <c r="E28" s="8">
         <v>1300</v>
       </c>
-      <c r="H28" s="35">
+      <c r="H28" s="32">
         <v>10000</v>
       </c>
-      <c r="M28" s="29"/>
-      <c r="N28" s="30">
+      <c r="N28" s="9">
         <v>242000</v>
       </c>
-      <c r="O28" s="31">
+      <c r="O28" s="29">
         <v>253000</v>
       </c>
-      <c r="P28" s="32">
+      <c r="P28" s="30">
         <v>174000</v>
       </c>
-      <c r="Q28" s="32">
+      <c r="Q28" s="30">
         <v>182000</v>
       </c>
-      <c r="R28" s="31">
+      <c r="R28" s="29">
         <v>160000</v>
       </c>
-      <c r="S28" s="32">
+      <c r="S28" s="30">
         <v>47500</v>
       </c>
-      <c r="T28" s="29">
+      <c r="T28" s="8">
         <v>135</v>
       </c>
-      <c r="U28" s="29">
+      <c r="U28" s="8">
         <v>510</v>
       </c>
-      <c r="V28" s="29">
+      <c r="V28" s="8">
         <v>380</v>
       </c>
-      <c r="W28" s="29"/>
     </row>
     <row r="29" spans="1:23">
       <c r="A29" s="7">
         <v>27</v>
       </c>
       <c r="B29" s="1"/>
-      <c r="C29" s="29">
+      <c r="C29" s="8">
         <v>1400</v>
       </c>
-      <c r="D29" s="33">
+      <c r="D29" s="1">
         <v>1335</v>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="8">
         <v>1350</v>
       </c>
-      <c r="H29" s="35">
+      <c r="H29" s="32">
         <v>10400</v>
       </c>
-      <c r="M29" s="29"/>
-      <c r="N29" s="30">
+      <c r="N29" s="9">
         <v>253000</v>
       </c>
-      <c r="O29" s="31">
+      <c r="O29" s="29">
         <v>264000</v>
       </c>
-      <c r="P29" s="32">
+      <c r="P29" s="30">
         <v>182000</v>
       </c>
-      <c r="Q29" s="32">
+      <c r="Q29" s="30">
         <v>190000</v>
       </c>
-      <c r="R29" s="31">
+      <c r="R29" s="29">
         <v>167000</v>
       </c>
-      <c r="S29" s="32">
+      <c r="S29" s="30">
         <v>49500</v>
       </c>
-      <c r="T29" s="29">
+      <c r="T29" s="8">
         <v>140</v>
       </c>
-      <c r="U29" s="29">
+      <c r="U29" s="8">
         <v>530</v>
       </c>
-      <c r="V29" s="29">
+      <c r="V29" s="8">
         <v>395</v>
       </c>
-      <c r="W29" s="29"/>
     </row>
     <row r="30" spans="1:23">
       <c r="A30" s="7">
         <v>28</v>
       </c>
       <c r="B30" s="1"/>
-      <c r="C30" s="29">
+      <c r="C30" s="8">
         <v>1450</v>
       </c>
-      <c r="D30" s="33">
+      <c r="D30" s="1">
         <v>1385</v>
       </c>
-      <c r="E30" s="29">
+      <c r="E30" s="8">
         <v>1400</v>
       </c>
-      <c r="H30" s="35">
+      <c r="H30" s="32">
         <v>10800</v>
       </c>
-      <c r="M30" s="29"/>
-      <c r="N30" s="30">
+      <c r="N30" s="9">
         <v>264000</v>
       </c>
-      <c r="O30" s="31">
+      <c r="O30" s="29">
         <v>275000</v>
       </c>
-      <c r="P30" s="32">
+      <c r="P30" s="30">
         <v>190000</v>
       </c>
-      <c r="Q30" s="32">
+      <c r="Q30" s="30">
         <v>198000</v>
       </c>
-      <c r="R30" s="31">
+      <c r="R30" s="29">
         <v>174000</v>
       </c>
-      <c r="S30" s="32">
+      <c r="S30" s="30">
         <v>51500</v>
       </c>
-      <c r="T30" s="29">
+      <c r="T30" s="8">
         <v>145</v>
       </c>
-      <c r="U30" s="29">
+      <c r="U30" s="8">
         <v>550</v>
       </c>
-      <c r="V30" s="29">
+      <c r="V30" s="8">
         <v>410</v>
       </c>
-      <c r="W30" s="29"/>
     </row>
     <row r="31" spans="1:23">
       <c r="A31" s="7">
         <v>29</v>
       </c>
       <c r="B31" s="1"/>
-      <c r="C31" s="29">
+      <c r="C31" s="8">
         <v>1500</v>
       </c>
-      <c r="D31" s="33">
+      <c r="D31" s="1">
         <v>1435</v>
       </c>
-      <c r="E31" s="29">
+      <c r="E31" s="8">
         <v>1450</v>
       </c>
-      <c r="H31" s="35">
+      <c r="H31" s="32">
         <v>11200</v>
       </c>
-      <c r="M31" s="29"/>
-      <c r="N31" s="30">
+      <c r="N31" s="9">
         <v>275000</v>
       </c>
-      <c r="O31" s="31">
+      <c r="O31" s="29">
         <v>286000</v>
       </c>
-      <c r="P31" s="32">
+      <c r="P31" s="30">
         <v>198000</v>
       </c>
-      <c r="Q31" s="32">
+      <c r="Q31" s="30">
         <v>206000</v>
       </c>
-      <c r="R31" s="31">
+      <c r="R31" s="29">
         <v>181000</v>
       </c>
-      <c r="S31" s="32">
+      <c r="S31" s="30">
         <v>53500</v>
       </c>
-      <c r="T31" s="29">
+      <c r="T31" s="8">
         <v>150</v>
       </c>
-      <c r="U31" s="29">
+      <c r="U31" s="8">
         <v>570</v>
       </c>
-      <c r="V31" s="29">
+      <c r="V31" s="8">
         <v>425</v>
       </c>
-      <c r="W31" s="29"/>
     </row>
     <row r="32" spans="1:23">
       <c r="A32" s="7">
         <v>30</v>
       </c>
       <c r="B32" s="1"/>
-      <c r="C32" s="29">
+      <c r="C32" s="8">
         <v>1530</v>
       </c>
-      <c r="D32" s="29">
+      <c r="D32" s="8">
         <v>1485</v>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="8">
         <v>1500</v>
       </c>
-      <c r="H32" s="35">
+      <c r="H32" s="32">
         <v>11600</v>
       </c>
-      <c r="M32" s="29"/>
-      <c r="N32" s="30">
+      <c r="N32" s="9">
         <v>286000</v>
       </c>
-      <c r="O32" s="31">
+      <c r="O32" s="29">
         <v>297000</v>
       </c>
-      <c r="P32" s="32">
+      <c r="P32" s="30">
         <v>206000</v>
       </c>
-      <c r="Q32" s="32">
+      <c r="Q32" s="30">
         <v>214000</v>
       </c>
-      <c r="R32" s="31">
+      <c r="R32" s="29">
         <v>188000</v>
       </c>
-      <c r="S32" s="32">
+      <c r="S32" s="30">
         <v>55500</v>
       </c>
-      <c r="T32" s="29">
+      <c r="T32" s="8">
         <v>155</v>
       </c>
-      <c r="U32" s="29">
+      <c r="U32" s="8">
         <v>590</v>
       </c>
-      <c r="V32" s="29">
+      <c r="V32" s="8">
         <v>440</v>
       </c>
-      <c r="W32" s="29"/>
     </row>
     <row r="33" spans="8:21">
       <c r="H33" s="23" t="s">
